--- a/dev/mapping_overview.xlsx
+++ b/dev/mapping_overview.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10427" uniqueCount="2435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10435" uniqueCount="2438">
   <si>
     <t>Key</t>
   </si>
@@ -5989,10 +5989,13 @@
     <t>ocean liming</t>
   </si>
   <si>
-    <t>bioenergy, with CCS</t>
-  </si>
-  <si>
-    <t>biomass industrial emissions with CCS</t>
+    <t>biomass power generation, with CCS</t>
+  </si>
+  <si>
+    <t>synthetic fuels, with CCS</t>
+  </si>
+  <si>
+    <t>biofuels, with CCS</t>
   </si>
   <si>
     <t>Emi|CO2|CDR|+|DACCS</t>
@@ -6058,10 +6061,16 @@
     <t>Emi|CO2|CDR|+|BECCS</t>
   </si>
   <si>
-    <t>Carbon Capture|Energy</t>
+    <t>Carbon Capture|Energy|Supply|Electricity|Biomass</t>
   </si>
   <si>
     <t>Emi|CO2|CDR|+|Synthetic Fuels CCS</t>
+  </si>
+  <si>
+    <t>Carbon Capture|Energy|Supply|Hydrogen|Biomass</t>
+  </si>
+  <si>
+    <t>Carbon Capture|Energy|Supply|Liquids|Biomass</t>
   </si>
   <si>
     <t>sugar</t>
@@ -13871,7 +13880,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -13896,7 +13905,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="D2" t="s">
         <v>330</v>
@@ -13910,7 +13919,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="D3" t="s">
         <v>330</v>
@@ -13924,7 +13933,7 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="D4" t="s">
         <v>330</v>
@@ -13938,7 +13947,7 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="D5" t="s">
         <v>330</v>
@@ -13952,7 +13961,7 @@
         <v>1290</v>
       </c>
       <c r="C6" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="D6" t="s">
         <v>330</v>
@@ -13966,7 +13975,7 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="D7" t="s">
         <v>330</v>
@@ -13980,7 +13989,7 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="D8" t="s">
         <v>330</v>
@@ -13994,7 +14003,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D9" t="s">
         <v>331</v>
@@ -14120,7 +14129,7 @@
         <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="D18" t="s">
         <v>331</v>
@@ -14134,7 +14143,7 @@
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="D19" t="s">
         <v>331</v>
@@ -14148,7 +14157,7 @@
         <v>1290</v>
       </c>
       <c r="C20" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="D20" t="s">
         <v>331</v>
@@ -14162,7 +14171,7 @@
         <v>1290</v>
       </c>
       <c r="C21" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="D21" t="s">
         <v>331</v>
@@ -14176,7 +14185,7 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="D22" t="s">
         <v>331</v>
@@ -14190,7 +14199,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D23" t="s">
         <v>331</v>
@@ -14204,7 +14213,7 @@
         <v>1290</v>
       </c>
       <c r="C24" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="D24" t="s">
         <v>330</v>
@@ -14218,7 +14227,7 @@
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D25" t="s">
         <v>330</v>
@@ -14232,7 +14241,7 @@
         <v>1290</v>
       </c>
       <c r="C26" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D26" t="s">
         <v>331</v>
@@ -14246,7 +14255,7 @@
         <v>1290</v>
       </c>
       <c r="C27" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D27" t="s">
         <v>331</v>
@@ -14260,7 +14269,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D28" t="s">
         <v>331</v>
@@ -14274,7 +14283,7 @@
         <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D29" t="s">
         <v>330</v>
@@ -14288,7 +14297,7 @@
         <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D30" t="s">
         <v>330</v>
@@ -14358,7 +14367,7 @@
         <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D35" t="s">
         <v>330</v>
@@ -14372,7 +14381,7 @@
         <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D36" t="s">
         <v>330</v>
@@ -14386,7 +14395,7 @@
         <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D37" t="s">
         <v>330</v>
@@ -14400,7 +14409,7 @@
         <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D38" t="s">
         <v>330</v>
@@ -14414,7 +14423,7 @@
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D39" t="s">
         <v>330</v>
@@ -14428,7 +14437,7 @@
         <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D40" t="s">
         <v>330</v>
@@ -14442,9 +14451,37 @@
         <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D41" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D42" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D43" t="s">
         <v>330</v>
       </c>
     </row>
@@ -14474,296 +14511,296 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D2" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D3" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D4" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D5" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="D6" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D7" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D8" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D9" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="D10" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D11" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="D12" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="D13" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="D14" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="D15" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="D16" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="D17" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="D18" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="D19" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="D20" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="D21" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="D22" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
     </row>
   </sheetData>
@@ -14792,13 +14829,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="D2" t="s">
         <v>330</v>
@@ -14806,13 +14843,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="D3" t="s">
         <v>330</v>
@@ -14820,13 +14857,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="D4" t="s">
         <v>330</v>
@@ -14834,13 +14871,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="D5" t="s">
         <v>330</v>
@@ -14848,13 +14885,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="D6" t="s">
         <v>330</v>
@@ -14862,13 +14899,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="D7" t="s">
         <v>331</v>
@@ -14876,13 +14913,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="D8" t="s">
         <v>331</v>
@@ -14890,7 +14927,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -14904,7 +14941,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
@@ -14918,7 +14955,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
@@ -14932,13 +14969,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="D12" t="s">
         <v>330</v>
@@ -14946,7 +14983,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
@@ -14960,13 +14997,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="D14" t="s">
         <v>330</v>
@@ -14974,7 +15011,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
@@ -14988,13 +15025,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="D16" t="s">
         <v>330</v>
@@ -15002,13 +15039,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="D17" t="s">
         <v>330</v>
@@ -15016,13 +15053,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="D18" t="s">
         <v>330</v>
@@ -15030,13 +15067,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="D19" t="s">
         <v>330</v>
@@ -15044,13 +15081,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="D20" t="s">
         <v>331</v>
@@ -15058,13 +15095,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="D21" t="s">
         <v>331</v>
@@ -15072,7 +15109,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
@@ -15086,7 +15123,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -15100,13 +15137,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="D24" t="s">
         <v>330</v>
@@ -15114,7 +15151,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
@@ -15128,13 +15165,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="D26" t="s">
         <v>330</v>
@@ -15142,13 +15179,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="D27" t="s">
         <v>330</v>
@@ -15156,13 +15193,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="B28" t="s">
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="D28" t="s">
         <v>330</v>
@@ -15170,13 +15207,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="D29" t="s">
         <v>330</v>
@@ -15184,13 +15221,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="D30" t="s">
         <v>331</v>
@@ -15198,13 +15235,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="D31" t="s">
         <v>331</v>
@@ -15212,7 +15249,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B32" t="s">
         <v>27</v>
@@ -15226,7 +15263,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B33" t="s">
         <v>22</v>
@@ -15240,13 +15277,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="B34" t="s">
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="D34" t="s">
         <v>330</v>
@@ -15254,13 +15291,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="D35" t="s">
         <v>330</v>
@@ -15268,13 +15305,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="D36" t="s">
         <v>330</v>
@@ -15282,7 +15319,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="B37" t="s">
         <v>23</v>
@@ -15296,7 +15333,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
@@ -15310,7 +15347,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="B39" t="s">
         <v>22</v>
@@ -15348,7 +15385,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -15362,7 +15399,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -15376,7 +15413,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -15390,7 +15427,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -15404,7 +15441,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -15418,7 +15455,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -15432,7 +15469,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -15446,7 +15483,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -15460,7 +15497,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
@@ -15474,7 +15511,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
@@ -15488,7 +15525,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
@@ -15502,7 +15539,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -15516,7 +15553,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -15530,7 +15567,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -15544,7 +15581,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -15558,7 +15595,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -15572,7 +15609,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -15586,7 +15623,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -15600,7 +15637,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -15614,7 +15651,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -15628,7 +15665,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
@@ -15642,7 +15679,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -15656,7 +15693,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -15670,7 +15707,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -15684,7 +15721,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
@@ -15698,7 +15735,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -15712,7 +15749,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="B28" t="s">
         <v>22</v>
@@ -15726,7 +15763,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
@@ -15740,7 +15777,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
@@ -15754,7 +15791,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="B31" t="s">
         <v>22</v>
@@ -15768,7 +15805,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="B32" t="s">
         <v>23</v>
@@ -15782,7 +15819,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -15796,7 +15833,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -15810,7 +15847,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
@@ -15824,7 +15861,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
@@ -15838,7 +15875,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="B37" t="s">
         <v>22</v>
@@ -15852,7 +15889,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="B38" t="s">
         <v>23</v>
@@ -15866,7 +15903,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
@@ -15880,7 +15917,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="B40" t="s">
         <v>22</v>
@@ -15894,7 +15931,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="B41" t="s">
         <v>22</v>
@@ -15908,7 +15945,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="B42" t="s">
         <v>22</v>
@@ -15922,7 +15959,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="B43" t="s">
         <v>22</v>
@@ -15936,7 +15973,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="B44" t="s">
         <v>23</v>
@@ -15950,7 +15987,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="B45" t="s">
         <v>24</v>
@@ -15964,7 +16001,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="B46" t="s">
         <v>23</v>
@@ -15978,7 +16015,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="B47" t="s">
         <v>24</v>
@@ -15992,7 +16029,7 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="B48" t="s">
         <v>22</v>
@@ -16006,7 +16043,7 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="B49" t="s">
         <v>22</v>
@@ -16020,7 +16057,7 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="B50" t="s">
         <v>22</v>
@@ -16034,7 +16071,7 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="B51" t="s">
         <v>22</v>
@@ -16048,7 +16085,7 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="B52" t="s">
         <v>23</v>
@@ -16062,7 +16099,7 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="B53" t="s">
         <v>24</v>
@@ -16076,7 +16113,7 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="B54" t="s">
         <v>22</v>
@@ -16090,7 +16127,7 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="B55" t="s">
         <v>22</v>
@@ -16104,7 +16141,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="B56" t="s">
         <v>22</v>
@@ -16118,7 +16155,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="B57" t="s">
         <v>22</v>
@@ -16132,7 +16169,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="B58" t="s">
         <v>22</v>
@@ -16146,13 +16183,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="B59" t="s">
         <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
       <c r="D59" t="s">
         <v>330</v>
@@ -16160,13 +16197,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="B60" t="s">
         <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
       <c r="D60" t="s">
         <v>330</v>
@@ -16174,7 +16211,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="B61" t="s">
         <v>22</v>
@@ -16188,13 +16225,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="B62" t="s">
         <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="D62" t="s">
         <v>330</v>
@@ -16202,13 +16239,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="B63" t="s">
         <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="D63" t="s">
         <v>330</v>
@@ -16216,7 +16253,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="B64" t="s">
         <v>22</v>
@@ -16230,13 +16267,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="B65" t="s">
         <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="D65" t="s">
         <v>330</v>
@@ -16244,13 +16281,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="B66" t="s">
         <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="D66" t="s">
         <v>330</v>
@@ -16258,7 +16295,7 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="B67" t="s">
         <v>22</v>
@@ -16272,13 +16309,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="B68" t="s">
         <v>23</v>
       </c>
       <c r="C68" t="s">
-        <v>2099</v>
+        <v>2102</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -16286,13 +16323,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="B69" t="s">
         <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>2099</v>
+        <v>2102</v>
       </c>
       <c r="D69" t="s">
         <v>330</v>
@@ -16300,7 +16337,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="B70" t="s">
         <v>22</v>
@@ -16314,7 +16351,7 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="B71" t="s">
         <v>22</v>
@@ -16328,13 +16365,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B72" t="s">
         <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
       <c r="D72" t="s">
         <v>330</v>
@@ -16342,13 +16379,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B73" t="s">
         <v>24</v>
       </c>
       <c r="C73" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
       <c r="D73" t="s">
         <v>330</v>
@@ -16356,13 +16393,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="B74" t="s">
         <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="D74" t="s">
         <v>330</v>
@@ -16370,13 +16407,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="B75" t="s">
         <v>24</v>
       </c>
       <c r="C75" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="D75" t="s">
         <v>330</v>
@@ -16384,7 +16421,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="B76" t="s">
         <v>23</v>
@@ -16398,7 +16435,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="B77" t="s">
         <v>24</v>
@@ -16412,7 +16449,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="B78" t="s">
         <v>23</v>
@@ -16426,7 +16463,7 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="B79" t="s">
         <v>24</v>
@@ -16440,13 +16477,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="B80" t="s">
         <v>1290</v>
       </c>
       <c r="C80" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D80" t="s">
         <v>330</v>
@@ -16454,7 +16491,7 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="B81" t="s">
         <v>23</v>
@@ -16468,7 +16505,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="B82" t="s">
         <v>24</v>
@@ -16482,13 +16519,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="B83" t="s">
         <v>27</v>
       </c>
       <c r="C83" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="D83" t="s">
         <v>330</v>
@@ -16496,7 +16533,7 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="B84" t="s">
         <v>23</v>
@@ -16510,7 +16547,7 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="B85" t="s">
         <v>24</v>
@@ -16524,13 +16561,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="B86" t="s">
         <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="D86" t="s">
         <v>330</v>
@@ -16538,13 +16575,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="B87" t="s">
         <v>1290</v>
       </c>
       <c r="C87" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D87" t="s">
         <v>330</v>
@@ -16552,13 +16589,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="B88" t="s">
         <v>1290</v>
       </c>
       <c r="C88" t="s">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="D88" t="s">
         <v>330</v>
@@ -16566,13 +16603,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="B89" t="s">
         <v>1290</v>
       </c>
       <c r="C89" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="D89" t="s">
         <v>330</v>
@@ -16580,13 +16617,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="B90" t="s">
         <v>1290</v>
       </c>
       <c r="C90" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="D90" t="s">
         <v>330</v>
@@ -16594,7 +16631,7 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="B91" t="s">
         <v>23</v>
@@ -16608,7 +16645,7 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="B92" t="s">
         <v>24</v>
@@ -16622,7 +16659,7 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="B93" t="s">
         <v>23</v>
@@ -16636,7 +16673,7 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="B94" t="s">
         <v>24</v>
@@ -16674,13 +16711,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="D2" t="s">
         <v>330</v>
@@ -16688,13 +16725,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="D3" t="s">
         <v>330</v>
@@ -16702,13 +16739,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="D4" t="s">
         <v>330</v>
@@ -16716,13 +16753,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>2219</v>
+        <v>2222</v>
       </c>
       <c r="D5" t="s">
         <v>330</v>
@@ -16730,13 +16767,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="D6" t="s">
         <v>330</v>
@@ -16744,13 +16781,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="B7" t="s">
         <v>1290</v>
       </c>
       <c r="C7" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
       <c r="D7" t="s">
         <v>330</v>
@@ -16758,13 +16795,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
       <c r="D8" t="s">
         <v>330</v>
@@ -16772,13 +16809,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="D9" t="s">
         <v>330</v>
@@ -16786,13 +16823,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="D10" t="s">
         <v>330</v>
@@ -16800,13 +16837,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="D11" t="s">
         <v>330</v>
@@ -16814,13 +16851,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="D12" t="s">
         <v>330</v>
@@ -16828,13 +16865,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="D13" t="s">
         <v>1739</v>
@@ -16842,13 +16879,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="D14" t="s">
         <v>1739</v>
@@ -16856,13 +16893,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
       <c r="D15" t="s">
         <v>330</v>
@@ -16870,13 +16907,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="D16" t="s">
         <v>330</v>
@@ -16884,13 +16921,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="D17" t="s">
         <v>330</v>
@@ -16898,13 +16935,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>2229</v>
+        <v>2232</v>
       </c>
       <c r="D18" t="s">
         <v>330</v>
@@ -16912,13 +16949,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
       <c r="D19" t="s">
         <v>330</v>
@@ -16926,13 +16963,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="B20" t="s">
         <v>1290</v>
       </c>
       <c r="C20" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="D20" t="s">
         <v>330</v>
@@ -16940,13 +16977,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="D21" t="s">
         <v>330</v>
@@ -16954,13 +16991,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
       <c r="D22" t="s">
         <v>330</v>
@@ -16968,13 +17005,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="D23" t="s">
         <v>330</v>
@@ -16982,13 +17019,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="D24" t="s">
         <v>330</v>
@@ -16996,13 +17033,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>2235</v>
+        <v>2238</v>
       </c>
       <c r="D25" t="s">
         <v>330</v>
@@ -17010,13 +17047,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
       <c r="D26" t="s">
         <v>330</v>
@@ -17024,13 +17061,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="B27" t="s">
         <v>1290</v>
       </c>
       <c r="C27" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="D27" t="s">
         <v>330</v>
@@ -17038,13 +17075,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="D28" t="s">
         <v>1739</v>
@@ -17052,13 +17089,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="B29" t="s">
         <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="D29" t="s">
         <v>1739</v>
@@ -17066,13 +17103,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="D30" t="s">
         <v>1739</v>
@@ -17080,13 +17117,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="B31" t="s">
         <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
       <c r="D31" t="s">
         <v>330</v>
@@ -17094,13 +17131,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="D32" t="s">
         <v>330</v>
@@ -17108,13 +17145,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="B33" t="s">
         <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="D33" t="s">
         <v>330</v>
@@ -17122,13 +17159,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="D34" t="s">
         <v>330</v>
@@ -17136,13 +17173,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>2243</v>
+        <v>2246</v>
       </c>
       <c r="D35" t="s">
         <v>330</v>
@@ -17150,13 +17187,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="B36" t="s">
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="D36" t="s">
         <v>330</v>
@@ -17164,13 +17201,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="B37" t="s">
         <v>1290</v>
       </c>
       <c r="C37" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="D37" t="s">
         <v>330</v>
@@ -17178,13 +17215,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="D38" t="s">
         <v>1739</v>
@@ -17192,13 +17229,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="D39" t="s">
         <v>1739</v>
@@ -17206,13 +17243,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="D40" t="s">
         <v>1739</v>
@@ -17220,13 +17257,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>2246</v>
+        <v>2249</v>
       </c>
       <c r="D41" t="s">
         <v>330</v>
@@ -17234,13 +17271,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="D42" t="s">
         <v>330</v>
@@ -17248,13 +17285,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="B43" t="s">
         <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="D43" t="s">
         <v>330</v>
@@ -17262,13 +17299,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="B44" t="s">
         <v>1290</v>
       </c>
       <c r="C44" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="D44" t="s">
         <v>330</v>
@@ -17276,13 +17313,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="B45" t="s">
         <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>2249</v>
+        <v>2252</v>
       </c>
       <c r="D45" t="s">
         <v>1739</v>
@@ -17290,13 +17327,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="B46" t="s">
         <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>2250</v>
+        <v>2253</v>
       </c>
       <c r="D46" t="s">
         <v>330</v>
@@ -17304,13 +17341,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="B47" t="s">
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="D47" t="s">
         <v>330</v>
@@ -17318,13 +17355,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="B48" t="s">
         <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="D48" t="s">
         <v>330</v>
@@ -17332,13 +17369,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="B49" t="s">
         <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
       <c r="D49" t="s">
         <v>330</v>
@@ -17346,13 +17383,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="B50" t="s">
         <v>1290</v>
       </c>
       <c r="C50" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
       <c r="D50" t="s">
         <v>330</v>
@@ -17360,13 +17397,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="B51" t="s">
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="D51" t="s">
         <v>1739</v>
@@ -17374,13 +17411,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="B52" t="s">
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>2255</v>
+        <v>2258</v>
       </c>
       <c r="D52" t="s">
         <v>330</v>
@@ -17388,13 +17425,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="B53" t="s">
         <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="D53" t="s">
         <v>330</v>
@@ -17402,13 +17439,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="B54" t="s">
         <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="D54" t="s">
         <v>330</v>
@@ -17416,13 +17453,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="B55" t="s">
         <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>2257</v>
+        <v>2260</v>
       </c>
       <c r="D55" t="s">
         <v>330</v>
@@ -17430,13 +17467,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="B56" t="s">
         <v>1290</v>
       </c>
       <c r="C56" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
       <c r="D56" t="s">
         <v>330</v>
@@ -17444,13 +17481,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="B57" t="s">
         <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="D57" t="s">
         <v>1739</v>
@@ -17458,13 +17495,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="B58" t="s">
         <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
       <c r="D58" t="s">
         <v>330</v>
@@ -17472,13 +17509,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="B59" t="s">
         <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
       <c r="D59" t="s">
         <v>330</v>
@@ -17486,13 +17523,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="B60" t="s">
         <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="D60" t="s">
         <v>330</v>
@@ -17500,13 +17537,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="B61" t="s">
         <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="D61" t="s">
         <v>330</v>
@@ -17514,13 +17551,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="B62" t="s">
         <v>1290</v>
       </c>
       <c r="C62" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="D62" t="s">
         <v>330</v>
@@ -17528,13 +17565,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
       <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="D63" t="s">
         <v>1739</v>
@@ -17542,13 +17579,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="B64" t="s">
         <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>2263</v>
+        <v>2266</v>
       </c>
       <c r="D64" t="s">
         <v>330</v>
@@ -17556,13 +17593,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="B65" t="s">
         <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>2250</v>
+        <v>2253</v>
       </c>
       <c r="D65" t="s">
         <v>330</v>
@@ -17570,13 +17607,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="B66" t="s">
         <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="D66" t="s">
         <v>330</v>
@@ -17584,13 +17621,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="B67" t="s">
         <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="D67" t="s">
         <v>330</v>
@@ -17598,13 +17635,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="B68" t="s">
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>2264</v>
+        <v>2267</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -17612,13 +17649,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="B69" t="s">
         <v>1290</v>
       </c>
       <c r="C69" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
       <c r="D69" t="s">
         <v>330</v>
@@ -17626,13 +17663,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="B70" t="s">
         <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="D70" t="s">
         <v>1739</v>
@@ -17640,13 +17677,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="B71" t="s">
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="D71" t="s">
         <v>1739</v>
@@ -17654,13 +17691,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="B72" t="s">
         <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="D72" t="s">
         <v>330</v>
@@ -17668,13 +17705,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="B73" t="s">
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>2255</v>
+        <v>2258</v>
       </c>
       <c r="D73" t="s">
         <v>330</v>
@@ -17682,13 +17719,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="B74" t="s">
         <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="D74" t="s">
         <v>330</v>
@@ -17696,13 +17733,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="B75" t="s">
         <v>24</v>
       </c>
       <c r="C75" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="D75" t="s">
         <v>330</v>
@@ -17710,13 +17747,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="B76" t="s">
         <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
       <c r="D76" t="s">
         <v>330</v>
@@ -17724,13 +17761,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="B77" t="s">
         <v>1290</v>
       </c>
       <c r="C77" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
       <c r="D77" t="s">
         <v>330</v>
@@ -17738,13 +17775,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>2123</v>
+        <v>2126</v>
       </c>
       <c r="B78" t="s">
         <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
       <c r="D78" t="s">
         <v>1739</v>
@@ -17752,13 +17789,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>2123</v>
+        <v>2126</v>
       </c>
       <c r="B79" t="s">
         <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="D79" t="s">
         <v>1739</v>
@@ -17766,13 +17803,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="B80" t="s">
         <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="D80" t="s">
         <v>330</v>
@@ -17780,13 +17817,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="B81" t="s">
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="D81" t="s">
         <v>330</v>
@@ -17794,13 +17831,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="B82" t="s">
         <v>23</v>
       </c>
       <c r="C82" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="D82" t="s">
         <v>330</v>
@@ -17808,13 +17845,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="B83" t="s">
         <v>24</v>
       </c>
       <c r="C83" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="D83" t="s">
         <v>330</v>
@@ -17822,13 +17859,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="B84" t="s">
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
       <c r="D84" t="s">
         <v>330</v>
@@ -17836,13 +17873,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="B85" t="s">
         <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
       <c r="D85" t="s">
         <v>330</v>
@@ -17850,13 +17887,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="B86" t="s">
         <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="D86" t="s">
         <v>1739</v>
@@ -17864,13 +17901,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="B87" t="s">
         <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="D87" t="s">
         <v>1739</v>
@@ -17878,13 +17915,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="B88" t="s">
         <v>22</v>
       </c>
       <c r="C88" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
       <c r="D88" t="s">
         <v>1739</v>
@@ -17892,13 +17929,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="B89" t="s">
         <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="D89" t="s">
         <v>330</v>
@@ -17906,13 +17943,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="B90" t="s">
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="D90" t="s">
         <v>330</v>
@@ -17920,13 +17957,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="B91" t="s">
         <v>23</v>
       </c>
       <c r="C91" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
       <c r="D91" t="s">
         <v>330</v>
@@ -17934,13 +17971,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="B92" t="s">
         <v>24</v>
       </c>
       <c r="C92" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
       <c r="D92" t="s">
         <v>330</v>
@@ -17948,13 +17985,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="B93" t="s">
         <v>22</v>
       </c>
       <c r="C93" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="D93" t="s">
         <v>330</v>
@@ -17962,13 +17999,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="B94" t="s">
         <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="D94" t="s">
         <v>330</v>
@@ -17976,13 +18013,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="B95" t="s">
         <v>27</v>
       </c>
       <c r="C95" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="D95" t="s">
         <v>1739</v>
@@ -17990,13 +18027,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="B96" t="s">
         <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="D96" t="s">
         <v>1739</v>
@@ -18004,13 +18041,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="B97" t="s">
         <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="D97" t="s">
         <v>1739</v>
@@ -18018,13 +18055,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>2128</v>
+        <v>2131</v>
       </c>
       <c r="B98" t="s">
         <v>22</v>
       </c>
       <c r="C98" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
       <c r="D98" t="s">
         <v>330</v>
@@ -18032,13 +18069,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="B99" t="s">
         <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="D99" t="s">
         <v>1739</v>
@@ -18046,13 +18083,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="B100" t="s">
         <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
       <c r="D100" t="s">
         <v>1739</v>
@@ -18060,13 +18097,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="B101" t="s">
         <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>2286</v>
+        <v>2289</v>
       </c>
       <c r="D101" t="s">
         <v>330</v>
@@ -18074,13 +18111,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B102" t="s">
         <v>26</v>
       </c>
       <c r="C102" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="D102" t="s">
         <v>1739</v>
@@ -18088,13 +18125,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B103" t="s">
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="D103" t="s">
         <v>1739</v>
@@ -18102,13 +18139,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="B104" t="s">
         <v>27</v>
       </c>
       <c r="C104" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="D104" t="s">
         <v>330</v>
@@ -18116,13 +18153,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="B105" t="s">
         <v>27</v>
       </c>
       <c r="C105" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="D105" t="s">
         <v>1739</v>
@@ -18130,13 +18167,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="B106" t="s">
         <v>27</v>
       </c>
       <c r="C106" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="D106" t="s">
         <v>330</v>
@@ -18144,13 +18181,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>2135</v>
+        <v>2138</v>
       </c>
       <c r="B107" t="s">
         <v>27</v>
       </c>
       <c r="C107" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="D107" t="s">
         <v>1739</v>
@@ -18158,13 +18195,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B108" t="s">
         <v>27</v>
       </c>
       <c r="C108" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="D108" t="s">
         <v>330</v>
@@ -18172,13 +18209,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B109" t="s">
         <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
       <c r="D109" t="s">
         <v>330</v>
@@ -18186,13 +18223,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B110" t="s">
         <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="D110" t="s">
         <v>330</v>
@@ -18200,13 +18237,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B111" t="s">
         <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="D111" t="s">
         <v>330</v>
@@ -18214,13 +18251,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B112" t="s">
         <v>22</v>
       </c>
       <c r="C112" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="D112" t="s">
         <v>330</v>
@@ -18228,13 +18265,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B113" t="s">
         <v>22</v>
       </c>
       <c r="C113" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="D113" t="s">
         <v>330</v>
@@ -18242,13 +18279,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B114" t="s">
         <v>25</v>
       </c>
       <c r="C114" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="D114" t="s">
         <v>330</v>
@@ -18256,13 +18293,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="B115" t="s">
         <v>1290</v>
       </c>
       <c r="C115" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
       <c r="D115" t="s">
         <v>330</v>
@@ -18270,13 +18307,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="B116" t="s">
         <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="D116" t="s">
         <v>1739</v>
@@ -18284,13 +18321,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="B117" t="s">
         <v>23</v>
       </c>
       <c r="C117" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="D117" t="s">
         <v>1739</v>
@@ -18298,13 +18335,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="B118" t="s">
         <v>24</v>
       </c>
       <c r="C118" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="D118" t="s">
         <v>1739</v>
@@ -18312,13 +18349,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="B119" t="s">
         <v>27</v>
       </c>
       <c r="C119" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="D119" t="s">
         <v>1739</v>
@@ -18326,13 +18363,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="B120" t="s">
         <v>1290</v>
       </c>
       <c r="C120" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="D120" t="s">
         <v>1739</v>
@@ -18340,13 +18377,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>2138</v>
+        <v>2141</v>
       </c>
       <c r="B121" t="s">
         <v>22</v>
       </c>
       <c r="C121" t="s">
-        <v>2299</v>
+        <v>2302</v>
       </c>
       <c r="D121" t="s">
         <v>330</v>
@@ -18354,13 +18391,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="B122" t="s">
         <v>22</v>
       </c>
       <c r="C122" t="s">
-        <v>2300</v>
+        <v>2303</v>
       </c>
       <c r="D122" t="s">
         <v>330</v>
@@ -18368,13 +18405,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>2140</v>
+        <v>2143</v>
       </c>
       <c r="B123" t="s">
         <v>22</v>
       </c>
       <c r="C123" t="s">
-        <v>2301</v>
+        <v>2304</v>
       </c>
       <c r="D123" t="s">
         <v>330</v>
@@ -18382,13 +18419,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="B124" t="s">
         <v>22</v>
       </c>
       <c r="C124" t="s">
-        <v>2302</v>
+        <v>2305</v>
       </c>
       <c r="D124" t="s">
         <v>330</v>
@@ -18396,13 +18433,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>2142</v>
+        <v>2145</v>
       </c>
       <c r="B125" t="s">
         <v>22</v>
       </c>
       <c r="C125" t="s">
-        <v>2303</v>
+        <v>2306</v>
       </c>
       <c r="D125" t="s">
         <v>330</v>
@@ -18410,13 +18447,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="B126" t="s">
         <v>1290</v>
       </c>
       <c r="C126" t="s">
-        <v>2304</v>
+        <v>2307</v>
       </c>
       <c r="D126" t="s">
         <v>330</v>
@@ -18424,13 +18461,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="B127" t="s">
         <v>1290</v>
       </c>
       <c r="C127" t="s">
-        <v>2305</v>
+        <v>2308</v>
       </c>
       <c r="D127" t="s">
         <v>1739</v>
@@ -18438,13 +18475,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="B128" t="s">
         <v>26</v>
       </c>
       <c r="C128" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="D128" t="s">
         <v>330</v>
@@ -18452,13 +18489,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="B129" t="s">
         <v>26</v>
       </c>
       <c r="C129" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
       <c r="D129" t="s">
         <v>1739</v>
@@ -18466,13 +18503,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="B130" t="s">
         <v>27</v>
       </c>
       <c r="C130" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
       <c r="D130" t="s">
         <v>330</v>
@@ -18480,13 +18517,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="B131" t="s">
         <v>26</v>
       </c>
       <c r="C131" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="D131" t="s">
         <v>330</v>
@@ -18494,13 +18531,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="B132" t="s">
         <v>23</v>
       </c>
       <c r="C132" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="D132" t="s">
         <v>330</v>
@@ -18508,13 +18545,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="B133" t="s">
         <v>24</v>
       </c>
       <c r="C133" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="D133" t="s">
         <v>330</v>
@@ -18522,13 +18559,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="B134" t="s">
         <v>22</v>
       </c>
       <c r="C134" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
       <c r="D134" t="s">
         <v>330</v>
@@ -18536,13 +18573,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="B135" t="s">
         <v>25</v>
       </c>
       <c r="C135" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
       <c r="D135" t="s">
         <v>330</v>
@@ -18550,13 +18587,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="B136" t="s">
         <v>26</v>
       </c>
       <c r="C136" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
       <c r="D136" t="s">
         <v>1739</v>
@@ -18564,13 +18601,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="B137" t="s">
         <v>23</v>
       </c>
       <c r="C137" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="D137" t="s">
         <v>1739</v>
@@ -18578,13 +18615,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="B138" t="s">
         <v>24</v>
       </c>
       <c r="C138" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="D138" t="s">
         <v>1739</v>
@@ -18592,13 +18629,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="B139" t="s">
         <v>27</v>
       </c>
       <c r="C139" t="s">
-        <v>2314</v>
+        <v>2317</v>
       </c>
       <c r="D139" t="s">
         <v>330</v>
@@ -18606,13 +18643,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="B140" t="s">
         <v>26</v>
       </c>
       <c r="C140" t="s">
-        <v>2315</v>
+        <v>2318</v>
       </c>
       <c r="D140" t="s">
         <v>330</v>
@@ -18620,13 +18657,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="B141" t="s">
         <v>23</v>
       </c>
       <c r="C141" t="s">
-        <v>2316</v>
+        <v>2319</v>
       </c>
       <c r="D141" t="s">
         <v>330</v>
@@ -18634,13 +18671,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="B142" t="s">
         <v>24</v>
       </c>
       <c r="C142" t="s">
-        <v>2316</v>
+        <v>2319</v>
       </c>
       <c r="D142" t="s">
         <v>330</v>
@@ -18648,13 +18685,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="B143" t="s">
         <v>22</v>
       </c>
       <c r="C143" t="s">
-        <v>2317</v>
+        <v>2320</v>
       </c>
       <c r="D143" t="s">
         <v>330</v>
@@ -18662,13 +18699,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="B144" t="s">
         <v>25</v>
       </c>
       <c r="C144" t="s">
-        <v>2317</v>
+        <v>2320</v>
       </c>
       <c r="D144" t="s">
         <v>330</v>
@@ -18676,13 +18713,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B145" t="s">
         <v>26</v>
       </c>
       <c r="C145" t="s">
-        <v>2318</v>
+        <v>2321</v>
       </c>
       <c r="D145" t="s">
         <v>1739</v>
@@ -18690,13 +18727,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B146" t="s">
         <v>23</v>
       </c>
       <c r="C146" t="s">
-        <v>2319</v>
+        <v>2322</v>
       </c>
       <c r="D146" t="s">
         <v>1739</v>
@@ -18704,13 +18741,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B147" t="s">
         <v>24</v>
       </c>
       <c r="C147" t="s">
-        <v>2319</v>
+        <v>2322</v>
       </c>
       <c r="D147" t="s">
         <v>1739</v>
@@ -18718,13 +18755,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="B148" t="s">
         <v>27</v>
       </c>
       <c r="C148" t="s">
-        <v>2320</v>
+        <v>2323</v>
       </c>
       <c r="D148" t="s">
         <v>330</v>
@@ -18732,13 +18769,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="B149" t="s">
         <v>23</v>
       </c>
       <c r="C149" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="D149" t="s">
         <v>330</v>
@@ -18746,13 +18783,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="B150" t="s">
         <v>24</v>
       </c>
       <c r="C150" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="D150" t="s">
         <v>330</v>
@@ -18760,13 +18797,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="B151" t="s">
         <v>22</v>
       </c>
       <c r="C151" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
       <c r="D151" t="s">
         <v>330</v>
@@ -18774,13 +18811,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="B152" t="s">
         <v>25</v>
       </c>
       <c r="C152" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
       <c r="D152" t="s">
         <v>330</v>
@@ -18788,13 +18825,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="B153" t="s">
         <v>23</v>
       </c>
       <c r="C153" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
       <c r="D153" t="s">
         <v>1739</v>
@@ -18802,13 +18839,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="B154" t="s">
         <v>24</v>
       </c>
       <c r="C154" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
       <c r="D154" t="s">
         <v>1739</v>
@@ -18816,13 +18853,13 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="B155" t="s">
         <v>27</v>
       </c>
       <c r="C155" t="s">
-        <v>2324</v>
+        <v>2327</v>
       </c>
       <c r="D155" t="s">
         <v>330</v>
@@ -18830,13 +18867,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="B156" t="s">
         <v>26</v>
       </c>
       <c r="C156" t="s">
-        <v>2325</v>
+        <v>2328</v>
       </c>
       <c r="D156" t="s">
         <v>330</v>
@@ -18844,13 +18881,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="B157" t="s">
         <v>23</v>
       </c>
       <c r="C157" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="D157" t="s">
         <v>330</v>
@@ -18858,13 +18895,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="B158" t="s">
         <v>24</v>
       </c>
       <c r="C158" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="D158" t="s">
         <v>330</v>
@@ -18872,13 +18909,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="B159" t="s">
         <v>22</v>
       </c>
       <c r="C159" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
       <c r="D159" t="s">
         <v>330</v>
@@ -18886,13 +18923,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="B160" t="s">
         <v>25</v>
       </c>
       <c r="C160" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
       <c r="D160" t="s">
         <v>330</v>
@@ -18900,13 +18937,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="B161" t="s">
         <v>26</v>
       </c>
       <c r="C161" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
       <c r="D161" t="s">
         <v>1739</v>
@@ -18914,13 +18951,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="B162" t="s">
         <v>23</v>
       </c>
       <c r="C162" t="s">
-        <v>2329</v>
+        <v>2332</v>
       </c>
       <c r="D162" t="s">
         <v>1739</v>
@@ -18928,13 +18965,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="B163" t="s">
         <v>24</v>
       </c>
       <c r="C163" t="s">
-        <v>2329</v>
+        <v>2332</v>
       </c>
       <c r="D163" t="s">
         <v>1739</v>
@@ -18942,13 +18979,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B164" t="s">
         <v>27</v>
       </c>
       <c r="C164" t="s">
-        <v>2330</v>
+        <v>2333</v>
       </c>
       <c r="D164" t="s">
         <v>330</v>
@@ -18956,13 +18993,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B165" t="s">
         <v>26</v>
       </c>
       <c r="C165" t="s">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="D165" t="s">
         <v>330</v>
@@ -18970,13 +19007,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B166" t="s">
         <v>23</v>
       </c>
       <c r="C166" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
       <c r="D166" t="s">
         <v>330</v>
@@ -18984,13 +19021,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B167" t="s">
         <v>24</v>
       </c>
       <c r="C167" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
       <c r="D167" t="s">
         <v>330</v>
@@ -18998,13 +19035,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B168" t="s">
         <v>22</v>
       </c>
       <c r="C168" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
       <c r="D168" t="s">
         <v>330</v>
@@ -19012,13 +19049,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B169" t="s">
         <v>25</v>
       </c>
       <c r="C169" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
       <c r="D169" t="s">
         <v>330</v>
@@ -19026,13 +19063,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B170" t="s">
         <v>1290</v>
       </c>
       <c r="C170" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
       <c r="D170" t="s">
         <v>330</v>
@@ -19040,13 +19077,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="B171" t="s">
         <v>26</v>
       </c>
       <c r="C171" t="s">
-        <v>2334</v>
+        <v>2337</v>
       </c>
       <c r="D171" t="s">
         <v>1739</v>
@@ -19054,13 +19091,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="B172" t="s">
         <v>23</v>
       </c>
       <c r="C172" t="s">
-        <v>2335</v>
+        <v>2338</v>
       </c>
       <c r="D172" t="s">
         <v>1739</v>
@@ -19068,13 +19105,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="B173" t="s">
         <v>24</v>
       </c>
       <c r="C173" t="s">
-        <v>2335</v>
+        <v>2338</v>
       </c>
       <c r="D173" t="s">
         <v>1739</v>
@@ -19082,13 +19119,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="B174" t="s">
         <v>1290</v>
       </c>
       <c r="C174" t="s">
-        <v>2336</v>
+        <v>2339</v>
       </c>
       <c r="D174" t="s">
         <v>1739</v>
@@ -19096,13 +19133,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="B175" t="s">
         <v>26</v>
       </c>
       <c r="C175" t="s">
-        <v>2337</v>
+        <v>2340</v>
       </c>
       <c r="D175" t="s">
         <v>330</v>
@@ -19110,13 +19147,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="B176" t="s">
         <v>23</v>
       </c>
       <c r="C176" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
       <c r="D176" t="s">
         <v>330</v>
@@ -19124,13 +19161,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="B177" t="s">
         <v>24</v>
       </c>
       <c r="C177" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
       <c r="D177" t="s">
         <v>330</v>
@@ -19138,13 +19175,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="B178" t="s">
         <v>22</v>
       </c>
       <c r="C178" t="s">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="D178" t="s">
         <v>330</v>
@@ -19152,13 +19189,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="B179" t="s">
         <v>25</v>
       </c>
       <c r="C179" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
       <c r="D179" t="s">
         <v>330</v>
@@ -19166,13 +19203,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="B180" t="s">
         <v>1290</v>
       </c>
       <c r="C180" t="s">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="D180" t="s">
         <v>330</v>
@@ -19180,13 +19217,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="B181" t="s">
         <v>26</v>
       </c>
       <c r="C181" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
       <c r="D181" t="s">
         <v>1739</v>
@@ -19194,13 +19231,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="B182" t="s">
         <v>23</v>
       </c>
       <c r="C182" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
       <c r="D182" t="s">
         <v>1739</v>
@@ -19208,13 +19245,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="B183" t="s">
         <v>24</v>
       </c>
       <c r="C183" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
       <c r="D183" t="s">
         <v>1739</v>
@@ -19222,13 +19259,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="B184" t="s">
         <v>1290</v>
       </c>
       <c r="C184" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="D184" t="s">
         <v>1739</v>
@@ -19236,13 +19273,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="B185" t="s">
         <v>22</v>
       </c>
       <c r="C185" t="s">
-        <v>2343</v>
+        <v>2346</v>
       </c>
       <c r="D185" t="s">
         <v>330</v>
@@ -19250,13 +19287,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="B186" t="s">
         <v>22</v>
       </c>
       <c r="C186" t="s">
-        <v>2344</v>
+        <v>2347</v>
       </c>
       <c r="D186" t="s">
         <v>330</v>
@@ -19264,13 +19301,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B187" t="s">
         <v>27</v>
       </c>
       <c r="C187" t="s">
-        <v>2345</v>
+        <v>2348</v>
       </c>
       <c r="D187" t="s">
         <v>330</v>
@@ -19278,13 +19315,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B188" t="s">
         <v>26</v>
       </c>
       <c r="C188" t="s">
-        <v>2346</v>
+        <v>2349</v>
       </c>
       <c r="D188" t="s">
         <v>330</v>
@@ -19292,13 +19329,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B189" t="s">
         <v>23</v>
       </c>
       <c r="C189" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
       <c r="D189" t="s">
         <v>330</v>
@@ -19306,13 +19343,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B190" t="s">
         <v>24</v>
       </c>
       <c r="C190" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
       <c r="D190" t="s">
         <v>330</v>
@@ -19320,13 +19357,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B191" t="s">
         <v>22</v>
       </c>
       <c r="C191" t="s">
-        <v>2348</v>
+        <v>2351</v>
       </c>
       <c r="D191" t="s">
         <v>330</v>
@@ -19334,13 +19371,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="B192" t="s">
         <v>27</v>
       </c>
       <c r="C192" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="D192" t="s">
         <v>1739</v>
@@ -19348,13 +19385,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="B193" t="s">
         <v>26</v>
       </c>
       <c r="C193" t="s">
-        <v>2349</v>
+        <v>2352</v>
       </c>
       <c r="D193" t="s">
         <v>1739</v>
@@ -19362,13 +19399,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="B194" t="s">
         <v>23</v>
       </c>
       <c r="C194" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="D194" t="s">
         <v>1739</v>
@@ -19376,13 +19413,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="B195" t="s">
         <v>24</v>
       </c>
       <c r="C195" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="D195" t="s">
         <v>1739</v>
@@ -19390,13 +19427,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="B196" t="s">
         <v>22</v>
       </c>
       <c r="C196" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="D196" t="s">
         <v>1739</v>
@@ -19404,13 +19441,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="B197" t="s">
         <v>27</v>
       </c>
       <c r="C197" t="s">
-        <v>2352</v>
+        <v>2355</v>
       </c>
       <c r="D197" t="s">
         <v>330</v>
@@ -19418,13 +19455,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="B198" t="s">
         <v>22</v>
       </c>
       <c r="C198" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="D198" t="s">
         <v>330</v>
@@ -19432,13 +19469,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="B199" t="s">
         <v>27</v>
       </c>
       <c r="C199" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="D199" t="s">
         <v>1739</v>
@@ -19446,13 +19483,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="B200" t="s">
         <v>22</v>
       </c>
       <c r="C200" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="D200" t="s">
         <v>1739</v>
@@ -19460,13 +19497,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="B201" t="s">
         <v>26</v>
       </c>
       <c r="C201" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="D201" t="s">
         <v>330</v>
@@ -19474,13 +19511,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="B202" t="s">
         <v>23</v>
       </c>
       <c r="C202" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="D202" t="s">
         <v>330</v>
@@ -19488,13 +19525,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="B203" t="s">
         <v>24</v>
       </c>
       <c r="C203" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="D203" t="s">
         <v>330</v>
@@ -19502,13 +19539,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="B204" t="s">
         <v>22</v>
       </c>
       <c r="C204" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="D204" t="s">
         <v>330</v>
@@ -19516,13 +19553,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="B205" t="s">
         <v>25</v>
       </c>
       <c r="C205" t="s">
-        <v>2358</v>
+        <v>2361</v>
       </c>
       <c r="D205" t="s">
         <v>330</v>
@@ -19530,13 +19567,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="B206" t="s">
         <v>1290</v>
       </c>
       <c r="C206" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="D206" t="s">
         <v>330</v>
@@ -19544,13 +19581,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="B207" t="s">
         <v>26</v>
       </c>
       <c r="C207" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="D207" t="s">
         <v>1739</v>
@@ -19558,13 +19595,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="B208" t="s">
         <v>23</v>
       </c>
       <c r="C208" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="D208" t="s">
         <v>1739</v>
@@ -19572,13 +19609,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="B209" t="s">
         <v>24</v>
       </c>
       <c r="C209" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="D209" t="s">
         <v>1739</v>
@@ -19586,13 +19623,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="B210" t="s">
         <v>22</v>
       </c>
       <c r="C210" t="s">
-        <v>2362</v>
+        <v>2365</v>
       </c>
       <c r="D210" t="s">
         <v>1739</v>
@@ -19600,13 +19637,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="B211" t="s">
         <v>26</v>
       </c>
       <c r="C211" t="s">
-        <v>2363</v>
+        <v>2366</v>
       </c>
       <c r="D211" t="s">
         <v>330</v>
@@ -19614,13 +19651,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="B212" t="s">
         <v>23</v>
       </c>
       <c r="C212" t="s">
-        <v>2364</v>
+        <v>2367</v>
       </c>
       <c r="D212" t="s">
         <v>330</v>
@@ -19628,13 +19665,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="B213" t="s">
         <v>24</v>
       </c>
       <c r="C213" t="s">
-        <v>2364</v>
+        <v>2367</v>
       </c>
       <c r="D213" t="s">
         <v>330</v>
@@ -19642,13 +19679,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="B214" t="s">
         <v>22</v>
       </c>
       <c r="C214" t="s">
-        <v>2365</v>
+        <v>2368</v>
       </c>
       <c r="D214" t="s">
         <v>330</v>
@@ -19656,13 +19693,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="B215" t="s">
         <v>25</v>
       </c>
       <c r="C215" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
       <c r="D215" t="s">
         <v>330</v>
@@ -19670,13 +19707,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="B216" t="s">
         <v>26</v>
       </c>
       <c r="C216" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
       <c r="D216" t="s">
         <v>1739</v>
@@ -19684,13 +19721,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="B217" t="s">
         <v>23</v>
       </c>
       <c r="C217" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="D217" t="s">
         <v>1739</v>
@@ -19698,13 +19735,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="B218" t="s">
         <v>24</v>
       </c>
       <c r="C218" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="D218" t="s">
         <v>1739</v>
@@ -19712,13 +19749,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="B219" t="s">
         <v>22</v>
       </c>
       <c r="C219" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
       <c r="D219" t="s">
         <v>1739</v>
@@ -19726,13 +19763,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="B220" t="s">
         <v>23</v>
       </c>
       <c r="C220" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="D220" t="s">
         <v>330</v>
@@ -19740,13 +19777,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="B221" t="s">
         <v>24</v>
       </c>
       <c r="C221" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="D221" t="s">
         <v>330</v>
@@ -19754,13 +19791,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="B222" t="s">
         <v>23</v>
       </c>
       <c r="C222" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="D222" t="s">
         <v>1739</v>
@@ -19768,13 +19805,13 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="B223" t="s">
         <v>24</v>
       </c>
       <c r="C223" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="D223" t="s">
         <v>1739</v>
@@ -19782,13 +19819,13 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="B224" t="s">
         <v>23</v>
       </c>
       <c r="C224" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="D224" t="s">
         <v>330</v>
@@ -19796,13 +19833,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="B225" t="s">
         <v>24</v>
       </c>
       <c r="C225" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="D225" t="s">
         <v>330</v>
@@ -19810,13 +19847,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="B226" t="s">
         <v>22</v>
       </c>
       <c r="C226" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
       <c r="D226" t="s">
         <v>330</v>
@@ -19824,13 +19861,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="B227" t="s">
         <v>23</v>
       </c>
       <c r="C227" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="D227" t="s">
         <v>1739</v>
@@ -19838,13 +19875,13 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="B228" t="s">
         <v>24</v>
       </c>
       <c r="C228" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="D228" t="s">
         <v>1739</v>
@@ -19852,13 +19889,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="B229" t="s">
         <v>22</v>
       </c>
       <c r="C229" t="s">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="D229" t="s">
         <v>1739</v>
@@ -19866,13 +19903,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>2173</v>
+        <v>2176</v>
       </c>
       <c r="B230" t="s">
         <v>22</v>
       </c>
       <c r="C230" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="D230" t="s">
         <v>330</v>
@@ -19880,13 +19917,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="B231" t="s">
         <v>22</v>
       </c>
       <c r="C231" t="s">
-        <v>2374</v>
+        <v>2377</v>
       </c>
       <c r="D231" t="s">
         <v>1739</v>
@@ -19894,13 +19931,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="B232" t="s">
         <v>26</v>
       </c>
       <c r="C232" t="s">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="D232" t="s">
         <v>330</v>
@@ -19908,13 +19945,13 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="B233" t="s">
         <v>22</v>
       </c>
       <c r="C233" t="s">
-        <v>2376</v>
+        <v>2379</v>
       </c>
       <c r="D233" t="s">
         <v>330</v>
@@ -19922,13 +19959,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="B234" t="s">
         <v>26</v>
       </c>
       <c r="C234" t="s">
-        <v>2377</v>
+        <v>2380</v>
       </c>
       <c r="D234" t="s">
         <v>1739</v>
@@ -19936,13 +19973,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="B235" t="s">
         <v>22</v>
       </c>
       <c r="C235" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
       <c r="D235" t="s">
         <v>1739</v>
@@ -19950,13 +19987,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="B236" t="s">
         <v>22</v>
       </c>
       <c r="C236" t="s">
-        <v>2379</v>
+        <v>2382</v>
       </c>
       <c r="D236" t="s">
         <v>330</v>
@@ -19964,13 +20001,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="B237" t="s">
         <v>22</v>
       </c>
       <c r="C237" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="D237" t="s">
         <v>1739</v>
@@ -19978,13 +20015,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="B238" t="s">
         <v>26</v>
       </c>
       <c r="C238" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="D238" t="s">
         <v>330</v>
@@ -19992,13 +20029,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="B239" t="s">
         <v>23</v>
       </c>
       <c r="C239" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="D239" t="s">
         <v>330</v>
@@ -20006,13 +20043,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="B240" t="s">
         <v>24</v>
       </c>
       <c r="C240" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="D240" t="s">
         <v>330</v>
@@ -20020,13 +20057,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="B241" t="s">
         <v>22</v>
       </c>
       <c r="C241" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
       <c r="D241" t="s">
         <v>330</v>
@@ -20034,13 +20071,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="B242" t="s">
         <v>1290</v>
       </c>
       <c r="C242" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="D242" t="s">
         <v>330</v>
@@ -20048,13 +20085,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="B243" t="s">
         <v>26</v>
       </c>
       <c r="C243" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="D243" t="s">
         <v>1739</v>
@@ -20062,13 +20099,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="B244" t="s">
         <v>23</v>
       </c>
       <c r="C244" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
       <c r="D244" t="s">
         <v>1739</v>
@@ -20076,13 +20113,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="B245" t="s">
         <v>24</v>
       </c>
       <c r="C245" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
       <c r="D245" t="s">
         <v>1739</v>
@@ -20090,13 +20127,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="B246" t="s">
         <v>22</v>
       </c>
       <c r="C246" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="D246" t="s">
         <v>1739</v>
@@ -20104,13 +20141,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="B247" t="s">
         <v>22</v>
       </c>
       <c r="C247" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="D247" t="s">
         <v>330</v>
@@ -20118,13 +20155,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="B248" t="s">
         <v>22</v>
       </c>
       <c r="C248" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
       <c r="D248" t="s">
         <v>1739</v>
@@ -20132,13 +20169,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="B249" t="s">
         <v>22</v>
       </c>
       <c r="C249" t="s">
-        <v>2390</v>
+        <v>2393</v>
       </c>
       <c r="D249" t="s">
         <v>330</v>
@@ -20146,13 +20183,13 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="B250" t="s">
         <v>25</v>
       </c>
       <c r="C250" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="D250" t="s">
         <v>330</v>
@@ -20160,13 +20197,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="B251" t="s">
         <v>22</v>
       </c>
       <c r="C251" t="s">
-        <v>2392</v>
+        <v>2395</v>
       </c>
       <c r="D251" t="s">
         <v>1739</v>
@@ -20174,13 +20211,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="B252" t="s">
         <v>22</v>
       </c>
       <c r="C252" t="s">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="D252" t="s">
         <v>330</v>
@@ -20188,13 +20225,13 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="B253" t="s">
         <v>22</v>
       </c>
       <c r="C253" t="s">
-        <v>2394</v>
+        <v>2397</v>
       </c>
       <c r="D253" t="s">
         <v>1739</v>
@@ -20202,13 +20239,13 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="B254" t="s">
         <v>22</v>
       </c>
       <c r="C254" t="s">
-        <v>2395</v>
+        <v>2398</v>
       </c>
       <c r="D254" t="s">
         <v>330</v>
@@ -20216,13 +20253,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="B255" t="s">
         <v>25</v>
       </c>
       <c r="C255" t="s">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="D255" t="s">
         <v>330</v>
@@ -20230,13 +20267,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="B256" t="s">
         <v>22</v>
       </c>
       <c r="C256" t="s">
-        <v>2397</v>
+        <v>2400</v>
       </c>
       <c r="D256" t="s">
         <v>1739</v>
@@ -20244,13 +20281,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="B257" t="s">
         <v>22</v>
       </c>
       <c r="C257" t="s">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="D257" t="s">
         <v>330</v>
@@ -20258,13 +20295,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="B258" t="s">
         <v>22</v>
       </c>
       <c r="C258" t="s">
-        <v>2399</v>
+        <v>2402</v>
       </c>
       <c r="D258" t="s">
         <v>1739</v>
@@ -20272,13 +20309,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="B259" t="s">
         <v>27</v>
       </c>
       <c r="C259" t="s">
-        <v>2400</v>
+        <v>2403</v>
       </c>
       <c r="D259" t="s">
         <v>330</v>
@@ -20286,13 +20323,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="B260" t="s">
         <v>27</v>
       </c>
       <c r="C260" t="s">
-        <v>2401</v>
+        <v>2404</v>
       </c>
       <c r="D260" t="s">
         <v>330</v>
@@ -20300,13 +20337,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="B261" t="s">
         <v>27</v>
       </c>
       <c r="C261" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="D261" t="s">
         <v>1739</v>
@@ -20314,13 +20351,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>2194</v>
+        <v>2197</v>
       </c>
       <c r="B262" t="s">
         <v>27</v>
       </c>
       <c r="C262" t="s">
-        <v>2402</v>
+        <v>2405</v>
       </c>
       <c r="D262" t="s">
         <v>330</v>
@@ -20328,13 +20365,13 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="B263" t="s">
         <v>27</v>
       </c>
       <c r="C263" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="D263" t="s">
         <v>1739</v>
@@ -20342,13 +20379,13 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>2196</v>
+        <v>2199</v>
       </c>
       <c r="B264" t="s">
         <v>27</v>
       </c>
       <c r="C264" t="s">
-        <v>2403</v>
+        <v>2406</v>
       </c>
       <c r="D264" t="s">
         <v>330</v>
@@ -20356,13 +20393,13 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>2197</v>
+        <v>2200</v>
       </c>
       <c r="B265" t="s">
         <v>27</v>
       </c>
       <c r="C265" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="D265" t="s">
         <v>1739</v>
@@ -20370,13 +20407,13 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="B266" t="s">
         <v>27</v>
       </c>
       <c r="C266" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="D266" t="s">
         <v>330</v>
@@ -20384,13 +20421,13 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>2199</v>
+        <v>2202</v>
       </c>
       <c r="B267" t="s">
         <v>27</v>
       </c>
       <c r="C267" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="D267" t="s">
         <v>1739</v>
@@ -20398,13 +20435,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>2200</v>
+        <v>2203</v>
       </c>
       <c r="B268" t="s">
         <v>27</v>
       </c>
       <c r="C268" t="s">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="D268" t="s">
         <v>330</v>
@@ -20412,13 +20449,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="B269" t="s">
         <v>27</v>
       </c>
       <c r="C269" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="D269" t="s">
         <v>1739</v>
@@ -20426,13 +20463,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="B270" t="s">
         <v>27</v>
       </c>
       <c r="C270" t="s">
-        <v>2406</v>
+        <v>2409</v>
       </c>
       <c r="D270" t="s">
         <v>330</v>
@@ -20440,13 +20477,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>2203</v>
+        <v>2206</v>
       </c>
       <c r="B271" t="s">
         <v>27</v>
       </c>
       <c r="C271" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
       <c r="D271" t="s">
         <v>1739</v>
@@ -20454,13 +20491,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>2204</v>
+        <v>2207</v>
       </c>
       <c r="B272" t="s">
         <v>27</v>
       </c>
       <c r="C272" t="s">
-        <v>2407</v>
+        <v>2410</v>
       </c>
       <c r="D272" t="s">
         <v>330</v>
@@ -20468,13 +20505,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>2205</v>
+        <v>2208</v>
       </c>
       <c r="B273" t="s">
         <v>27</v>
       </c>
       <c r="C273" t="s">
-        <v>2408</v>
+        <v>2411</v>
       </c>
       <c r="D273" t="s">
         <v>330</v>
@@ -20482,13 +20519,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="B274" t="s">
         <v>27</v>
       </c>
       <c r="C274" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="D274" t="s">
         <v>1739</v>
@@ -20496,13 +20533,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>2207</v>
+        <v>2210</v>
       </c>
       <c r="B275" t="s">
         <v>27</v>
       </c>
       <c r="C275" t="s">
-        <v>2409</v>
+        <v>2412</v>
       </c>
       <c r="D275" t="s">
         <v>330</v>
@@ -20510,13 +20547,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>2208</v>
+        <v>2211</v>
       </c>
       <c r="B276" t="s">
         <v>27</v>
       </c>
       <c r="C276" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
       <c r="D276" t="s">
         <v>1739</v>
@@ -20524,13 +20561,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="B277" t="s">
         <v>27</v>
       </c>
       <c r="C277" t="s">
-        <v>2410</v>
+        <v>2413</v>
       </c>
       <c r="D277" t="s">
         <v>330</v>
@@ -20538,13 +20575,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>2210</v>
+        <v>2213</v>
       </c>
       <c r="B278" t="s">
         <v>27</v>
       </c>
       <c r="C278" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="D278" t="s">
         <v>1739</v>
@@ -20552,13 +20589,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
       <c r="B279" t="s">
         <v>27</v>
       </c>
       <c r="C279" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
       <c r="D279" t="s">
         <v>330</v>
@@ -20566,13 +20603,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="B280" t="s">
         <v>27</v>
       </c>
       <c r="C280" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="D280" t="s">
         <v>1739</v>
@@ -20580,13 +20617,13 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="B281" t="s">
         <v>27</v>
       </c>
       <c r="C281" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="D281" t="s">
         <v>330</v>
@@ -20594,13 +20631,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>2214</v>
+        <v>2217</v>
       </c>
       <c r="B282" t="s">
         <v>27</v>
       </c>
       <c r="C282" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="D282" t="s">
         <v>1739</v>
@@ -20608,13 +20645,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>2215</v>
+        <v>2218</v>
       </c>
       <c r="B283" t="s">
         <v>27</v>
       </c>
       <c r="C283" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="D283" t="s">
         <v>330</v>
@@ -20622,13 +20659,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="B284" t="s">
         <v>27</v>
       </c>
       <c r="C284" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="D284" t="s">
         <v>1739</v>
@@ -20660,13 +20697,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="D2" t="s">
         <v>330</v>
@@ -20674,13 +20711,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="D3" t="s">
         <v>330</v>
@@ -20688,13 +20725,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="D4" t="s">
         <v>331</v>
@@ -20702,13 +20739,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="D5" t="s">
         <v>331</v>
@@ -20716,13 +20753,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="D6" t="s">
         <v>330</v>
@@ -20730,13 +20767,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="D7" t="s">
         <v>330</v>
@@ -20744,7 +20781,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -20758,7 +20795,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -20772,13 +20809,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
       <c r="D10" t="s">
         <v>330</v>
@@ -20786,13 +20823,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
       <c r="D11" t="s">
         <v>330</v>
@@ -20800,13 +20837,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>2430</v>
+        <v>2433</v>
       </c>
       <c r="D12" t="s">
         <v>331</v>
@@ -20814,13 +20851,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>2430</v>
+        <v>2433</v>
       </c>
       <c r="D13" t="s">
         <v>331</v>
@@ -20828,13 +20865,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="D14" t="s">
         <v>330</v>
@@ -20842,13 +20879,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="D15" t="s">
         <v>330</v>
@@ -20856,7 +20893,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
@@ -20870,7 +20907,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -20884,13 +20921,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="D18" t="s">
         <v>330</v>
@@ -20898,13 +20935,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="D19" t="s">
         <v>330</v>
@@ -20912,13 +20949,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="D20" t="s">
         <v>331</v>
@@ -20926,13 +20963,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="D21" t="s">
         <v>331</v>
@@ -20940,13 +20977,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
       <c r="D22" t="s">
         <v>330</v>
@@ -20954,13 +20991,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
       <c r="D23" t="s">
         <v>330</v>
@@ -20968,7 +21005,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -20982,7 +21019,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>

--- a/dev/mapping_overview.xlsx
+++ b/dev/mapping_overview.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10435" uniqueCount="2438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10435" uniqueCount="2440">
   <si>
     <t>Key</t>
   </si>
@@ -595,7 +595,7 @@
     <t>Production|Steel|Secondary|DRI and EAF 3</t>
   </si>
   <si>
-    <t>Production|Industry|Steel|Primary|EAF with DRI</t>
+    <t>Production|Industry|Steel|Secondary|EAF with DRI</t>
   </si>
   <si>
     <t>Final Energy|Industry|Iron and Steel|DRI EAF|Coal</t>
@@ -688,7 +688,7 @@
     <t>Production|Steel|Secondary|DRI and EAF 2|w CCS</t>
   </si>
   <si>
-    <t>Production|Industry|Steel|Primary|EAF with DRI CCS</t>
+    <t>Production|Industry|Steel|Secondary|EAF with DRI CCS</t>
   </si>
   <si>
     <t>Final Energy|Industry|Iron and Steel|DRI EAF + CCS|Coal</t>
@@ -754,7 +754,7 @@
     <t>Production|Industry|Steel|+|DRI-H2-EAF</t>
   </si>
   <si>
-    <t>Production|Industry|Steel|Primary|BLASTFUR with hydrogen</t>
+    <t>Production|Industry|Steel|Secondary|Hydrogen-based DRI</t>
   </si>
   <si>
     <t>Final Energy|Industry|Iron and Steel|H-DRI/EAF|Coal</t>
@@ -922,7 +922,7 @@
     <t>Production|Secondary|Steel</t>
   </si>
   <si>
-    <t>Production|Industry|Steel|Secondary</t>
+    <t>Production|Industry|Steel|Secondary|EAF with scrap</t>
   </si>
   <si>
     <t>Production|Steel|Secondary|EAF 1</t>
@@ -5863,6 +5863,9 @@
     <t>Production|Non-Metallic Minerals|Cement</t>
   </si>
   <si>
+    <t>Production|Industry|Cement|cement</t>
+  </si>
+  <si>
     <t>Production|Cement</t>
   </si>
   <si>
@@ -5948,6 +5951,9 @@
   </si>
   <si>
     <t>Production|Non-Metallic Minerals|Cement w CCS</t>
+  </si>
+  <si>
+    <t>Production|Industry|Cement|cement CCS</t>
   </si>
   <si>
     <t>FE|Industry|+++|Cement w CCS</t>
@@ -12761,7 +12767,7 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="D6" t="s">
         <v>330</v>
@@ -12775,7 +12781,7 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="D7" t="s">
         <v>330</v>
@@ -12789,7 +12795,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="D8" t="s">
         <v>331</v>
@@ -12803,7 +12809,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="D9" t="s">
         <v>331</v>
@@ -12929,7 +12935,7 @@
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="D18" t="s">
         <v>331</v>
@@ -12943,7 +12949,7 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D19" t="s">
         <v>331</v>
@@ -12957,7 +12963,7 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="D20" t="s">
         <v>331</v>
@@ -12971,7 +12977,7 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="D21" t="s">
         <v>331</v>
@@ -12985,7 +12991,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="D22" t="s">
         <v>331</v>
@@ -12999,7 +13005,7 @@
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="D23" t="s">
         <v>331</v>
@@ -13013,7 +13019,7 @@
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="D24" t="s">
         <v>331</v>
@@ -13027,7 +13033,7 @@
         <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="D25" t="s">
         <v>331</v>
@@ -13041,7 +13047,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="D26" t="s">
         <v>331</v>
@@ -13055,7 +13061,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="D27" t="s">
         <v>331</v>
@@ -13069,7 +13075,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="D28" t="s">
         <v>331</v>
@@ -13083,7 +13089,7 @@
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="D29" t="s">
         <v>331</v>
@@ -13097,7 +13103,7 @@
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="D30" t="s">
         <v>331</v>
@@ -13111,7 +13117,7 @@
         <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="D31" t="s">
         <v>331</v>
@@ -13125,7 +13131,7 @@
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="D32" t="s">
         <v>331</v>
@@ -13139,7 +13145,7 @@
         <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="D33" t="s">
         <v>331</v>
@@ -13153,7 +13159,7 @@
         <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="D34" t="s">
         <v>331</v>
@@ -13167,7 +13173,7 @@
         <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="D35" t="s">
         <v>331</v>
@@ -13181,7 +13187,7 @@
         <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="D36" t="s">
         <v>331</v>
@@ -13195,7 +13201,7 @@
         <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="D37" t="s">
         <v>331</v>
@@ -13209,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="D38" t="s">
         <v>331</v>
@@ -13223,7 +13229,7 @@
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="D39" t="s">
         <v>330</v>
@@ -13349,7 +13355,7 @@
         <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D48" t="s">
         <v>330</v>
@@ -13475,7 +13481,7 @@
         <v>22</v>
       </c>
       <c r="C57" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D57" t="s">
         <v>330</v>
@@ -13601,7 +13607,7 @@
         <v>22</v>
       </c>
       <c r="C66" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D66" t="s">
         <v>330</v>
@@ -13615,7 +13621,7 @@
         <v>23</v>
       </c>
       <c r="C67" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="D67" t="s">
         <v>330</v>
@@ -13629,7 +13635,7 @@
         <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -13643,7 +13649,7 @@
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="D69" t="s">
         <v>330</v>
@@ -13657,7 +13663,7 @@
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="D70" t="s">
         <v>330</v>
@@ -13671,7 +13677,7 @@
         <v>23</v>
       </c>
       <c r="C71" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="D71" t="s">
         <v>331</v>
@@ -13685,7 +13691,7 @@
         <v>24</v>
       </c>
       <c r="C72" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="D72" t="s">
         <v>331</v>
@@ -13811,7 +13817,7 @@
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="D81" t="s">
         <v>331</v>
@@ -13825,7 +13831,7 @@
         <v>26</v>
       </c>
       <c r="C82" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="D82" t="s">
         <v>331</v>
@@ -13839,7 +13845,7 @@
         <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="D83" t="s">
         <v>331</v>
@@ -13853,7 +13859,7 @@
         <v>26</v>
       </c>
       <c r="C84" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="D84" t="s">
         <v>331</v>
@@ -13867,7 +13873,7 @@
         <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="D85" t="s">
         <v>331</v>
@@ -13899,13 +13905,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="D2" t="s">
         <v>330</v>
@@ -13913,13 +13919,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="D3" t="s">
         <v>330</v>
@@ -13927,13 +13933,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="D4" t="s">
         <v>330</v>
@@ -13941,13 +13947,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="D5" t="s">
         <v>330</v>
@@ -13955,13 +13961,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B6" t="s">
         <v>1290</v>
       </c>
       <c r="C6" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="D6" t="s">
         <v>330</v>
@@ -13969,13 +13975,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="D7" t="s">
         <v>330</v>
@@ -13983,13 +13989,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="D8" t="s">
         <v>330</v>
@@ -13997,13 +14003,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="D9" t="s">
         <v>331</v>
@@ -14011,7 +14017,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
@@ -14025,7 +14031,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
@@ -14039,7 +14045,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
@@ -14053,7 +14059,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
@@ -14067,7 +14073,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -14081,7 +14087,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -14095,7 +14101,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -14109,7 +14115,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -14123,13 +14129,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="D18" t="s">
         <v>331</v>
@@ -14137,13 +14143,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="D19" t="s">
         <v>331</v>
@@ -14151,13 +14157,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B20" t="s">
         <v>1290</v>
       </c>
       <c r="C20" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="D20" t="s">
         <v>331</v>
@@ -14165,13 +14171,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B21" t="s">
         <v>1290</v>
       </c>
       <c r="C21" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="D21" t="s">
         <v>331</v>
@@ -14179,13 +14185,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="D22" t="s">
         <v>331</v>
@@ -14193,13 +14199,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="D23" t="s">
         <v>331</v>
@@ -14207,13 +14213,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="B24" t="s">
         <v>1290</v>
       </c>
       <c r="C24" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="D24" t="s">
         <v>330</v>
@@ -14221,13 +14227,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="D25" t="s">
         <v>330</v>
@@ -14235,13 +14241,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B26" t="s">
         <v>1290</v>
       </c>
       <c r="C26" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="D26" t="s">
         <v>331</v>
@@ -14249,13 +14255,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B27" t="s">
         <v>1290</v>
       </c>
       <c r="C27" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="D27" t="s">
         <v>331</v>
@@ -14263,13 +14269,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="D28" t="s">
         <v>331</v>
@@ -14277,13 +14283,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="B29" t="s">
         <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="D29" t="s">
         <v>330</v>
@@ -14291,13 +14297,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="D30" t="s">
         <v>330</v>
@@ -14305,7 +14311,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="B31" t="s">
         <v>23</v>
@@ -14319,7 +14325,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="B32" t="s">
         <v>23</v>
@@ -14333,7 +14339,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -14347,7 +14353,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -14361,13 +14367,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="D35" t="s">
         <v>330</v>
@@ -14375,13 +14381,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="D36" t="s">
         <v>330</v>
@@ -14389,13 +14395,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="B37" t="s">
         <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D37" t="s">
         <v>330</v>
@@ -14403,13 +14409,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D38" t="s">
         <v>330</v>
@@ -14417,13 +14423,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="B39" t="s">
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="D39" t="s">
         <v>330</v>
@@ -14431,13 +14437,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="B40" t="s">
         <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="D40" t="s">
         <v>330</v>
@@ -14445,13 +14451,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="B41" t="s">
         <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="D41" t="s">
         <v>330</v>
@@ -14459,13 +14465,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="B42" t="s">
         <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="D42" t="s">
         <v>330</v>
@@ -14473,13 +14479,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="B43" t="s">
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="D43" t="s">
         <v>330</v>
@@ -14511,296 +14517,296 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D2" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D3" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D6" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D7" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D8" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="D9" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="D10" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="D11" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="D12" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="D13" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="D14" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="D15" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="D16" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="D17" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="D18" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="D19" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="D20" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="D21" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="D22" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
     </row>
   </sheetData>
@@ -14829,13 +14835,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="D2" t="s">
         <v>330</v>
@@ -14843,13 +14849,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="D3" t="s">
         <v>330</v>
@@ -14857,13 +14863,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="D4" t="s">
         <v>330</v>
@@ -14871,13 +14877,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="D5" t="s">
         <v>330</v>
@@ -14885,13 +14891,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="D6" t="s">
         <v>330</v>
@@ -14899,13 +14905,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="D7" t="s">
         <v>331</v>
@@ -14913,13 +14919,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="D8" t="s">
         <v>331</v>
@@ -14927,7 +14933,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -14941,7 +14947,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
@@ -14955,7 +14961,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
@@ -14969,13 +14975,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="D12" t="s">
         <v>330</v>
@@ -14983,7 +14989,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
@@ -14997,13 +15003,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="D14" t="s">
         <v>330</v>
@@ -15011,7 +15017,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
@@ -15025,13 +15031,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="D16" t="s">
         <v>330</v>
@@ -15039,13 +15045,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="D17" t="s">
         <v>330</v>
@@ -15053,13 +15059,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="D18" t="s">
         <v>330</v>
@@ -15067,13 +15073,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="D19" t="s">
         <v>330</v>
@@ -15081,13 +15087,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="D20" t="s">
         <v>331</v>
@@ -15095,13 +15101,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="D21" t="s">
         <v>331</v>
@@ -15109,7 +15115,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
@@ -15123,7 +15129,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -15137,13 +15143,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="D24" t="s">
         <v>330</v>
@@ -15151,7 +15157,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
@@ -15165,13 +15171,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="D26" t="s">
         <v>330</v>
@@ -15179,13 +15185,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="D27" t="s">
         <v>330</v>
@@ -15193,13 +15199,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="B28" t="s">
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="D28" t="s">
         <v>330</v>
@@ -15207,13 +15213,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="D29" t="s">
         <v>330</v>
@@ -15221,13 +15227,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="D30" t="s">
         <v>331</v>
@@ -15235,13 +15241,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="D31" t="s">
         <v>331</v>
@@ -15249,7 +15255,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="B32" t="s">
         <v>27</v>
@@ -15263,7 +15269,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="B33" t="s">
         <v>22</v>
@@ -15277,13 +15283,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="B34" t="s">
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="D34" t="s">
         <v>330</v>
@@ -15291,13 +15297,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="D35" t="s">
         <v>330</v>
@@ -15305,13 +15311,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="D36" t="s">
         <v>330</v>
@@ -15319,7 +15325,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B37" t="s">
         <v>23</v>
@@ -15333,7 +15339,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
@@ -15347,7 +15353,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B39" t="s">
         <v>22</v>
@@ -15385,7 +15391,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -15399,7 +15405,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -15413,7 +15419,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -15427,7 +15433,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -15441,7 +15447,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -15455,7 +15461,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -15469,7 +15475,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -15483,7 +15489,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -15497,7 +15503,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
@@ -15511,7 +15517,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
@@ -15525,7 +15531,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
@@ -15539,7 +15545,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -15553,7 +15559,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -15567,7 +15573,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -15581,7 +15587,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -15595,7 +15601,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -15609,7 +15615,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -15623,7 +15629,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -15637,7 +15643,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -15651,7 +15657,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -15665,7 +15671,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
@@ -15679,7 +15685,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -15693,7 +15699,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -15707,7 +15713,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -15721,7 +15727,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
@@ -15735,7 +15741,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -15749,7 +15755,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="B28" t="s">
         <v>22</v>
@@ -15763,7 +15769,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
@@ -15777,7 +15783,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
@@ -15791,7 +15797,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="B31" t="s">
         <v>22</v>
@@ -15805,7 +15811,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B32" t="s">
         <v>23</v>
@@ -15819,7 +15825,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -15833,7 +15839,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -15847,7 +15853,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
@@ -15861,7 +15867,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
@@ -15875,7 +15881,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B37" t="s">
         <v>22</v>
@@ -15889,7 +15895,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="B38" t="s">
         <v>23</v>
@@ -15903,7 +15909,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
@@ -15917,7 +15923,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="B40" t="s">
         <v>22</v>
@@ -15931,7 +15937,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="B41" t="s">
         <v>22</v>
@@ -15945,7 +15951,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="B42" t="s">
         <v>22</v>
@@ -15959,7 +15965,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="B43" t="s">
         <v>22</v>
@@ -15973,7 +15979,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="B44" t="s">
         <v>23</v>
@@ -15987,7 +15993,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="B45" t="s">
         <v>24</v>
@@ -16001,7 +16007,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="B46" t="s">
         <v>23</v>
@@ -16015,7 +16021,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="B47" t="s">
         <v>24</v>
@@ -16029,7 +16035,7 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="B48" t="s">
         <v>22</v>
@@ -16043,7 +16049,7 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="B49" t="s">
         <v>22</v>
@@ -16057,7 +16063,7 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="B50" t="s">
         <v>22</v>
@@ -16071,7 +16077,7 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="B51" t="s">
         <v>22</v>
@@ -16085,7 +16091,7 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="B52" t="s">
         <v>23</v>
@@ -16099,7 +16105,7 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="B53" t="s">
         <v>24</v>
@@ -16113,7 +16119,7 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="B54" t="s">
         <v>22</v>
@@ -16127,7 +16133,7 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="B55" t="s">
         <v>22</v>
@@ -16141,7 +16147,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="B56" t="s">
         <v>22</v>
@@ -16155,7 +16161,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="B57" t="s">
         <v>22</v>
@@ -16169,7 +16175,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="B58" t="s">
         <v>22</v>
@@ -16183,13 +16189,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="B59" t="s">
         <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="D59" t="s">
         <v>330</v>
@@ -16197,13 +16203,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="B60" t="s">
         <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="D60" t="s">
         <v>330</v>
@@ -16211,7 +16217,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="B61" t="s">
         <v>22</v>
@@ -16225,13 +16231,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="B62" t="s">
         <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="D62" t="s">
         <v>330</v>
@@ -16239,13 +16245,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="B63" t="s">
         <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="D63" t="s">
         <v>330</v>
@@ -16253,7 +16259,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="B64" t="s">
         <v>22</v>
@@ -16267,13 +16273,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="B65" t="s">
         <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="D65" t="s">
         <v>330</v>
@@ -16281,13 +16287,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="B66" t="s">
         <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="D66" t="s">
         <v>330</v>
@@ -16295,7 +16301,7 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="B67" t="s">
         <v>22</v>
@@ -16309,13 +16315,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="B68" t="s">
         <v>23</v>
       </c>
       <c r="C68" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -16323,13 +16329,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="B69" t="s">
         <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="D69" t="s">
         <v>330</v>
@@ -16337,7 +16343,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="B70" t="s">
         <v>22</v>
@@ -16351,7 +16357,7 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="B71" t="s">
         <v>22</v>
@@ -16365,13 +16371,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="B72" t="s">
         <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="D72" t="s">
         <v>330</v>
@@ -16379,13 +16385,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="B73" t="s">
         <v>24</v>
       </c>
       <c r="C73" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="D73" t="s">
         <v>330</v>
@@ -16393,13 +16399,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="B74" t="s">
         <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="D74" t="s">
         <v>330</v>
@@ -16407,13 +16413,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="B75" t="s">
         <v>24</v>
       </c>
       <c r="C75" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="D75" t="s">
         <v>330</v>
@@ -16421,7 +16427,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="B76" t="s">
         <v>23</v>
@@ -16435,7 +16441,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="B77" t="s">
         <v>24</v>
@@ -16449,7 +16455,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="B78" t="s">
         <v>23</v>
@@ -16463,7 +16469,7 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="B79" t="s">
         <v>24</v>
@@ -16477,13 +16483,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="B80" t="s">
         <v>1290</v>
       </c>
       <c r="C80" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="D80" t="s">
         <v>330</v>
@@ -16491,7 +16497,7 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="B81" t="s">
         <v>23</v>
@@ -16505,7 +16511,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="B82" t="s">
         <v>24</v>
@@ -16519,13 +16525,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="B83" t="s">
         <v>27</v>
       </c>
       <c r="C83" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="D83" t="s">
         <v>330</v>
@@ -16533,7 +16539,7 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B84" t="s">
         <v>23</v>
@@ -16547,7 +16553,7 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B85" t="s">
         <v>24</v>
@@ -16561,13 +16567,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B86" t="s">
         <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="D86" t="s">
         <v>330</v>
@@ -16575,13 +16581,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B87" t="s">
         <v>1290</v>
       </c>
       <c r="C87" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="D87" t="s">
         <v>330</v>
@@ -16589,13 +16595,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B88" t="s">
         <v>1290</v>
       </c>
       <c r="C88" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="D88" t="s">
         <v>330</v>
@@ -16603,13 +16609,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B89" t="s">
         <v>1290</v>
       </c>
       <c r="C89" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="D89" t="s">
         <v>330</v>
@@ -16617,13 +16623,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B90" t="s">
         <v>1290</v>
       </c>
       <c r="C90" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="D90" t="s">
         <v>330</v>
@@ -16631,7 +16637,7 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="B91" t="s">
         <v>23</v>
@@ -16645,7 +16651,7 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="B92" t="s">
         <v>24</v>
@@ -16659,7 +16665,7 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="B93" t="s">
         <v>23</v>
@@ -16673,7 +16679,7 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="B94" t="s">
         <v>24</v>
@@ -16711,13 +16717,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="D2" t="s">
         <v>330</v>
@@ -16725,13 +16731,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="D3" t="s">
         <v>330</v>
@@ -16739,13 +16745,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="D4" t="s">
         <v>330</v>
@@ -16753,13 +16759,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="D5" t="s">
         <v>330</v>
@@ -16767,13 +16773,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="D6" t="s">
         <v>330</v>
@@ -16781,13 +16787,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B7" t="s">
         <v>1290</v>
       </c>
       <c r="C7" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="D7" t="s">
         <v>330</v>
@@ -16795,13 +16801,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="D8" t="s">
         <v>330</v>
@@ -16809,13 +16815,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="D9" t="s">
         <v>330</v>
@@ -16823,13 +16829,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="D10" t="s">
         <v>330</v>
@@ -16837,13 +16843,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="D11" t="s">
         <v>330</v>
@@ -16851,13 +16857,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D12" t="s">
         <v>330</v>
@@ -16865,13 +16871,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="D13" t="s">
         <v>1739</v>
@@ -16879,13 +16885,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="D14" t="s">
         <v>1739</v>
@@ -16893,13 +16899,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="D15" t="s">
         <v>330</v>
@@ -16907,13 +16913,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="D16" t="s">
         <v>330</v>
@@ -16921,13 +16927,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="D17" t="s">
         <v>330</v>
@@ -16935,13 +16941,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D18" t="s">
         <v>330</v>
@@ -16949,13 +16955,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="D19" t="s">
         <v>330</v>
@@ -16963,13 +16969,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="B20" t="s">
         <v>1290</v>
       </c>
       <c r="C20" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="D20" t="s">
         <v>330</v>
@@ -16977,13 +16983,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="D21" t="s">
         <v>330</v>
@@ -16991,13 +16997,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="D22" t="s">
         <v>330</v>
@@ -17005,13 +17011,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="D23" t="s">
         <v>330</v>
@@ -17019,13 +17025,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="D24" t="s">
         <v>330</v>
@@ -17033,13 +17039,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="D25" t="s">
         <v>330</v>
@@ -17047,13 +17053,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="D26" t="s">
         <v>330</v>
@@ -17061,13 +17067,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B27" t="s">
         <v>1290</v>
       </c>
       <c r="C27" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="D27" t="s">
         <v>330</v>
@@ -17075,13 +17081,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="D28" t="s">
         <v>1739</v>
@@ -17089,13 +17095,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="B29" t="s">
         <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="D29" t="s">
         <v>1739</v>
@@ -17103,13 +17109,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="D30" t="s">
         <v>1739</v>
@@ -17117,13 +17123,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B31" t="s">
         <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="D31" t="s">
         <v>330</v>
@@ -17131,13 +17137,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="D32" t="s">
         <v>330</v>
@@ -17145,13 +17151,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B33" t="s">
         <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="D33" t="s">
         <v>330</v>
@@ -17159,13 +17165,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="D34" t="s">
         <v>330</v>
@@ -17173,13 +17179,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="D35" t="s">
         <v>330</v>
@@ -17187,13 +17193,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B36" t="s">
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="D36" t="s">
         <v>330</v>
@@ -17201,13 +17207,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B37" t="s">
         <v>1290</v>
       </c>
       <c r="C37" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="D37" t="s">
         <v>330</v>
@@ -17215,13 +17221,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="D38" t="s">
         <v>1739</v>
@@ -17229,13 +17235,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="D39" t="s">
         <v>1739</v>
@@ -17243,13 +17249,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="D40" t="s">
         <v>1739</v>
@@ -17257,13 +17263,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="D41" t="s">
         <v>330</v>
@@ -17271,13 +17277,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="D42" t="s">
         <v>330</v>
@@ -17285,13 +17291,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="B43" t="s">
         <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="D43" t="s">
         <v>330</v>
@@ -17299,13 +17305,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="B44" t="s">
         <v>1290</v>
       </c>
       <c r="C44" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="D44" t="s">
         <v>330</v>
@@ -17313,13 +17319,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="B45" t="s">
         <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="D45" t="s">
         <v>1739</v>
@@ -17327,13 +17333,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="B46" t="s">
         <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="D46" t="s">
         <v>330</v>
@@ -17341,13 +17347,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="B47" t="s">
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="D47" t="s">
         <v>330</v>
@@ -17355,13 +17361,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="B48" t="s">
         <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="D48" t="s">
         <v>330</v>
@@ -17369,13 +17375,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="B49" t="s">
         <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="D49" t="s">
         <v>330</v>
@@ -17383,13 +17389,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="B50" t="s">
         <v>1290</v>
       </c>
       <c r="C50" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="D50" t="s">
         <v>330</v>
@@ -17397,13 +17403,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="B51" t="s">
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="D51" t="s">
         <v>1739</v>
@@ -17411,13 +17417,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="B52" t="s">
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="D52" t="s">
         <v>330</v>
@@ -17425,13 +17431,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="B53" t="s">
         <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="D53" t="s">
         <v>330</v>
@@ -17439,13 +17445,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="B54" t="s">
         <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="D54" t="s">
         <v>330</v>
@@ -17453,13 +17459,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="B55" t="s">
         <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="D55" t="s">
         <v>330</v>
@@ -17467,13 +17473,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="B56" t="s">
         <v>1290</v>
       </c>
       <c r="C56" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="D56" t="s">
         <v>330</v>
@@ -17481,13 +17487,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="B57" t="s">
         <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="D57" t="s">
         <v>1739</v>
@@ -17495,13 +17501,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="B58" t="s">
         <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="D58" t="s">
         <v>330</v>
@@ -17509,13 +17515,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="B59" t="s">
         <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="D59" t="s">
         <v>330</v>
@@ -17523,13 +17529,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="B60" t="s">
         <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="D60" t="s">
         <v>330</v>
@@ -17537,13 +17543,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="B61" t="s">
         <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="D61" t="s">
         <v>330</v>
@@ -17551,13 +17557,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="B62" t="s">
         <v>1290</v>
       </c>
       <c r="C62" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="D62" t="s">
         <v>330</v>
@@ -17565,13 +17571,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="D63" t="s">
         <v>1739</v>
@@ -17579,13 +17585,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="B64" t="s">
         <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="D64" t="s">
         <v>330</v>
@@ -17593,13 +17599,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="B65" t="s">
         <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="D65" t="s">
         <v>330</v>
@@ -17607,13 +17613,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="B66" t="s">
         <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="D66" t="s">
         <v>330</v>
@@ -17621,13 +17627,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="B67" t="s">
         <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="D67" t="s">
         <v>330</v>
@@ -17635,13 +17641,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="B68" t="s">
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -17649,13 +17655,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="B69" t="s">
         <v>1290</v>
       </c>
       <c r="C69" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="D69" t="s">
         <v>330</v>
@@ -17663,13 +17669,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="B70" t="s">
         <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="D70" t="s">
         <v>1739</v>
@@ -17677,13 +17683,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="B71" t="s">
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="D71" t="s">
         <v>1739</v>
@@ -17691,13 +17697,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="B72" t="s">
         <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="D72" t="s">
         <v>330</v>
@@ -17705,13 +17711,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="B73" t="s">
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="D73" t="s">
         <v>330</v>
@@ -17719,13 +17725,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="B74" t="s">
         <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="D74" t="s">
         <v>330</v>
@@ -17733,13 +17739,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="B75" t="s">
         <v>24</v>
       </c>
       <c r="C75" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="D75" t="s">
         <v>330</v>
@@ -17747,13 +17753,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="B76" t="s">
         <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="D76" t="s">
         <v>330</v>
@@ -17761,13 +17767,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="B77" t="s">
         <v>1290</v>
       </c>
       <c r="C77" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="D77" t="s">
         <v>330</v>
@@ -17775,13 +17781,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="B78" t="s">
         <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="D78" t="s">
         <v>1739</v>
@@ -17789,13 +17795,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="B79" t="s">
         <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="D79" t="s">
         <v>1739</v>
@@ -17803,13 +17809,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="B80" t="s">
         <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="D80" t="s">
         <v>330</v>
@@ -17817,13 +17823,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="B81" t="s">
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="D81" t="s">
         <v>330</v>
@@ -17831,13 +17837,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="B82" t="s">
         <v>23</v>
       </c>
       <c r="C82" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="D82" t="s">
         <v>330</v>
@@ -17845,13 +17851,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="B83" t="s">
         <v>24</v>
       </c>
       <c r="C83" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="D83" t="s">
         <v>330</v>
@@ -17859,13 +17865,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="B84" t="s">
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="D84" t="s">
         <v>330</v>
@@ -17873,13 +17879,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="B85" t="s">
         <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="D85" t="s">
         <v>330</v>
@@ -17887,13 +17893,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="B86" t="s">
         <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="D86" t="s">
         <v>1739</v>
@@ -17901,13 +17907,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="B87" t="s">
         <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="D87" t="s">
         <v>1739</v>
@@ -17915,13 +17921,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="B88" t="s">
         <v>22</v>
       </c>
       <c r="C88" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="D88" t="s">
         <v>1739</v>
@@ -17929,13 +17935,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="B89" t="s">
         <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="D89" t="s">
         <v>330</v>
@@ -17943,13 +17949,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="B90" t="s">
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="D90" t="s">
         <v>330</v>
@@ -17957,13 +17963,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="B91" t="s">
         <v>23</v>
       </c>
       <c r="C91" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="D91" t="s">
         <v>330</v>
@@ -17971,13 +17977,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="B92" t="s">
         <v>24</v>
       </c>
       <c r="C92" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="D92" t="s">
         <v>330</v>
@@ -17985,13 +17991,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="B93" t="s">
         <v>22</v>
       </c>
       <c r="C93" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="D93" t="s">
         <v>330</v>
@@ -17999,13 +18005,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="B94" t="s">
         <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="D94" t="s">
         <v>330</v>
@@ -18013,13 +18019,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="B95" t="s">
         <v>27</v>
       </c>
       <c r="C95" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="D95" t="s">
         <v>1739</v>
@@ -18027,13 +18033,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="B96" t="s">
         <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="D96" t="s">
         <v>1739</v>
@@ -18041,13 +18047,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="B97" t="s">
         <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="D97" t="s">
         <v>1739</v>
@@ -18055,13 +18061,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="B98" t="s">
         <v>22</v>
       </c>
       <c r="C98" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="D98" t="s">
         <v>330</v>
@@ -18069,13 +18075,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="B99" t="s">
         <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="D99" t="s">
         <v>1739</v>
@@ -18083,13 +18089,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="B100" t="s">
         <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="D100" t="s">
         <v>1739</v>
@@ -18097,13 +18103,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="B101" t="s">
         <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="D101" t="s">
         <v>330</v>
@@ -18111,13 +18117,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="B102" t="s">
         <v>26</v>
       </c>
       <c r="C102" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="D102" t="s">
         <v>1739</v>
@@ -18125,13 +18131,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="B103" t="s">
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="D103" t="s">
         <v>1739</v>
@@ -18139,13 +18145,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="B104" t="s">
         <v>27</v>
       </c>
       <c r="C104" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="D104" t="s">
         <v>330</v>
@@ -18153,13 +18159,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="B105" t="s">
         <v>27</v>
       </c>
       <c r="C105" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="D105" t="s">
         <v>1739</v>
@@ -18167,13 +18173,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="B106" t="s">
         <v>27</v>
       </c>
       <c r="C106" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="D106" t="s">
         <v>330</v>
@@ -18181,13 +18187,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="B107" t="s">
         <v>27</v>
       </c>
       <c r="C107" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="D107" t="s">
         <v>1739</v>
@@ -18195,13 +18201,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B108" t="s">
         <v>27</v>
       </c>
       <c r="C108" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="D108" t="s">
         <v>330</v>
@@ -18209,13 +18215,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B109" t="s">
         <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="D109" t="s">
         <v>330</v>
@@ -18223,13 +18229,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B110" t="s">
         <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="D110" t="s">
         <v>330</v>
@@ -18237,13 +18243,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B111" t="s">
         <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="D111" t="s">
         <v>330</v>
@@ -18251,13 +18257,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B112" t="s">
         <v>22</v>
       </c>
       <c r="C112" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="D112" t="s">
         <v>330</v>
@@ -18265,13 +18271,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B113" t="s">
         <v>22</v>
       </c>
       <c r="C113" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="D113" t="s">
         <v>330</v>
@@ -18279,13 +18285,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B114" t="s">
         <v>25</v>
       </c>
       <c r="C114" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="D114" t="s">
         <v>330</v>
@@ -18293,13 +18299,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B115" t="s">
         <v>1290</v>
       </c>
       <c r="C115" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="D115" t="s">
         <v>330</v>
@@ -18307,13 +18313,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="B116" t="s">
         <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="D116" t="s">
         <v>1739</v>
@@ -18321,13 +18327,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="B117" t="s">
         <v>23</v>
       </c>
       <c r="C117" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="D117" t="s">
         <v>1739</v>
@@ -18335,13 +18341,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="B118" t="s">
         <v>24</v>
       </c>
       <c r="C118" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="D118" t="s">
         <v>1739</v>
@@ -18349,13 +18355,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="B119" t="s">
         <v>27</v>
       </c>
       <c r="C119" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="D119" t="s">
         <v>1739</v>
@@ -18363,13 +18369,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="B120" t="s">
         <v>1290</v>
       </c>
       <c r="C120" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="D120" t="s">
         <v>1739</v>
@@ -18377,13 +18383,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="B121" t="s">
         <v>22</v>
       </c>
       <c r="C121" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="D121" t="s">
         <v>330</v>
@@ -18391,13 +18397,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="B122" t="s">
         <v>22</v>
       </c>
       <c r="C122" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="D122" t="s">
         <v>330</v>
@@ -18405,13 +18411,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="B123" t="s">
         <v>22</v>
       </c>
       <c r="C123" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="D123" t="s">
         <v>330</v>
@@ -18419,13 +18425,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="B124" t="s">
         <v>22</v>
       </c>
       <c r="C124" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="D124" t="s">
         <v>330</v>
@@ -18433,13 +18439,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="B125" t="s">
         <v>22</v>
       </c>
       <c r="C125" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="D125" t="s">
         <v>330</v>
@@ -18447,13 +18453,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="B126" t="s">
         <v>1290</v>
       </c>
       <c r="C126" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="D126" t="s">
         <v>330</v>
@@ -18461,13 +18467,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="B127" t="s">
         <v>1290</v>
       </c>
       <c r="C127" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="D127" t="s">
         <v>1739</v>
@@ -18475,13 +18481,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="B128" t="s">
         <v>26</v>
       </c>
       <c r="C128" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="D128" t="s">
         <v>330</v>
@@ -18489,13 +18495,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="B129" t="s">
         <v>26</v>
       </c>
       <c r="C129" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="D129" t="s">
         <v>1739</v>
@@ -18503,13 +18509,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="B130" t="s">
         <v>27</v>
       </c>
       <c r="C130" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="D130" t="s">
         <v>330</v>
@@ -18517,13 +18523,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="B131" t="s">
         <v>26</v>
       </c>
       <c r="C131" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="D131" t="s">
         <v>330</v>
@@ -18531,13 +18537,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="B132" t="s">
         <v>23</v>
       </c>
       <c r="C132" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="D132" t="s">
         <v>330</v>
@@ -18545,13 +18551,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="B133" t="s">
         <v>24</v>
       </c>
       <c r="C133" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="D133" t="s">
         <v>330</v>
@@ -18559,13 +18565,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="B134" t="s">
         <v>22</v>
       </c>
       <c r="C134" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="D134" t="s">
         <v>330</v>
@@ -18573,13 +18579,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="B135" t="s">
         <v>25</v>
       </c>
       <c r="C135" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="D135" t="s">
         <v>330</v>
@@ -18587,13 +18593,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="B136" t="s">
         <v>26</v>
       </c>
       <c r="C136" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="D136" t="s">
         <v>1739</v>
@@ -18601,13 +18607,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="B137" t="s">
         <v>23</v>
       </c>
       <c r="C137" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="D137" t="s">
         <v>1739</v>
@@ -18615,13 +18621,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="B138" t="s">
         <v>24</v>
       </c>
       <c r="C138" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="D138" t="s">
         <v>1739</v>
@@ -18629,13 +18635,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="B139" t="s">
         <v>27</v>
       </c>
       <c r="C139" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="D139" t="s">
         <v>330</v>
@@ -18643,13 +18649,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="B140" t="s">
         <v>26</v>
       </c>
       <c r="C140" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="D140" t="s">
         <v>330</v>
@@ -18657,13 +18663,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="B141" t="s">
         <v>23</v>
       </c>
       <c r="C141" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="D141" t="s">
         <v>330</v>
@@ -18671,13 +18677,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="B142" t="s">
         <v>24</v>
       </c>
       <c r="C142" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="D142" t="s">
         <v>330</v>
@@ -18685,13 +18691,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="B143" t="s">
         <v>22</v>
       </c>
       <c r="C143" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="D143" t="s">
         <v>330</v>
@@ -18699,13 +18705,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="B144" t="s">
         <v>25</v>
       </c>
       <c r="C144" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="D144" t="s">
         <v>330</v>
@@ -18713,13 +18719,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="B145" t="s">
         <v>26</v>
       </c>
       <c r="C145" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="D145" t="s">
         <v>1739</v>
@@ -18727,13 +18733,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="B146" t="s">
         <v>23</v>
       </c>
       <c r="C146" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="D146" t="s">
         <v>1739</v>
@@ -18741,13 +18747,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="B147" t="s">
         <v>24</v>
       </c>
       <c r="C147" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="D147" t="s">
         <v>1739</v>
@@ -18755,13 +18761,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="B148" t="s">
         <v>27</v>
       </c>
       <c r="C148" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="D148" t="s">
         <v>330</v>
@@ -18769,13 +18775,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="B149" t="s">
         <v>23</v>
       </c>
       <c r="C149" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="D149" t="s">
         <v>330</v>
@@ -18783,13 +18789,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="B150" t="s">
         <v>24</v>
       </c>
       <c r="C150" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="D150" t="s">
         <v>330</v>
@@ -18797,13 +18803,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="B151" t="s">
         <v>22</v>
       </c>
       <c r="C151" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="D151" t="s">
         <v>330</v>
@@ -18811,13 +18817,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="B152" t="s">
         <v>25</v>
       </c>
       <c r="C152" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="D152" t="s">
         <v>330</v>
@@ -18825,13 +18831,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="B153" t="s">
         <v>23</v>
       </c>
       <c r="C153" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="D153" t="s">
         <v>1739</v>
@@ -18839,13 +18845,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="B154" t="s">
         <v>24</v>
       </c>
       <c r="C154" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="D154" t="s">
         <v>1739</v>
@@ -18853,13 +18859,13 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="B155" t="s">
         <v>27</v>
       </c>
       <c r="C155" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="D155" t="s">
         <v>330</v>
@@ -18867,13 +18873,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="B156" t="s">
         <v>26</v>
       </c>
       <c r="C156" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="D156" t="s">
         <v>330</v>
@@ -18881,13 +18887,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="B157" t="s">
         <v>23</v>
       </c>
       <c r="C157" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="D157" t="s">
         <v>330</v>
@@ -18895,13 +18901,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="B158" t="s">
         <v>24</v>
       </c>
       <c r="C158" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="D158" t="s">
         <v>330</v>
@@ -18909,13 +18915,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="B159" t="s">
         <v>22</v>
       </c>
       <c r="C159" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="D159" t="s">
         <v>330</v>
@@ -18923,13 +18929,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="B160" t="s">
         <v>25</v>
       </c>
       <c r="C160" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="D160" t="s">
         <v>330</v>
@@ -18937,13 +18943,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="B161" t="s">
         <v>26</v>
       </c>
       <c r="C161" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="D161" t="s">
         <v>1739</v>
@@ -18951,13 +18957,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="B162" t="s">
         <v>23</v>
       </c>
       <c r="C162" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="D162" t="s">
         <v>1739</v>
@@ -18965,13 +18971,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="B163" t="s">
         <v>24</v>
       </c>
       <c r="C163" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="D163" t="s">
         <v>1739</v>
@@ -18979,13 +18985,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="B164" t="s">
         <v>27</v>
       </c>
       <c r="C164" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="D164" t="s">
         <v>330</v>
@@ -18993,13 +18999,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="B165" t="s">
         <v>26</v>
       </c>
       <c r="C165" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="D165" t="s">
         <v>330</v>
@@ -19007,13 +19013,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="B166" t="s">
         <v>23</v>
       </c>
       <c r="C166" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="D166" t="s">
         <v>330</v>
@@ -19021,13 +19027,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="B167" t="s">
         <v>24</v>
       </c>
       <c r="C167" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="D167" t="s">
         <v>330</v>
@@ -19035,13 +19041,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="B168" t="s">
         <v>22</v>
       </c>
       <c r="C168" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="D168" t="s">
         <v>330</v>
@@ -19049,13 +19055,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="B169" t="s">
         <v>25</v>
       </c>
       <c r="C169" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="D169" t="s">
         <v>330</v>
@@ -19063,13 +19069,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="B170" t="s">
         <v>1290</v>
       </c>
       <c r="C170" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="D170" t="s">
         <v>330</v>
@@ -19077,13 +19083,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="B171" t="s">
         <v>26</v>
       </c>
       <c r="C171" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="D171" t="s">
         <v>1739</v>
@@ -19091,13 +19097,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="B172" t="s">
         <v>23</v>
       </c>
       <c r="C172" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="D172" t="s">
         <v>1739</v>
@@ -19105,13 +19111,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="B173" t="s">
         <v>24</v>
       </c>
       <c r="C173" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="D173" t="s">
         <v>1739</v>
@@ -19119,13 +19125,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="B174" t="s">
         <v>1290</v>
       </c>
       <c r="C174" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="D174" t="s">
         <v>1739</v>
@@ -19133,13 +19139,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="B175" t="s">
         <v>26</v>
       </c>
       <c r="C175" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="D175" t="s">
         <v>330</v>
@@ -19147,13 +19153,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="B176" t="s">
         <v>23</v>
       </c>
       <c r="C176" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="D176" t="s">
         <v>330</v>
@@ -19161,13 +19167,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="B177" t="s">
         <v>24</v>
       </c>
       <c r="C177" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="D177" t="s">
         <v>330</v>
@@ -19175,13 +19181,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="B178" t="s">
         <v>22</v>
       </c>
       <c r="C178" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="D178" t="s">
         <v>330</v>
@@ -19189,13 +19195,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="B179" t="s">
         <v>25</v>
       </c>
       <c r="C179" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="D179" t="s">
         <v>330</v>
@@ -19203,13 +19209,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="B180" t="s">
         <v>1290</v>
       </c>
       <c r="C180" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="D180" t="s">
         <v>330</v>
@@ -19217,13 +19223,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="B181" t="s">
         <v>26</v>
       </c>
       <c r="C181" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="D181" t="s">
         <v>1739</v>
@@ -19231,13 +19237,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="B182" t="s">
         <v>23</v>
       </c>
       <c r="C182" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="D182" t="s">
         <v>1739</v>
@@ -19245,13 +19251,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="B183" t="s">
         <v>24</v>
       </c>
       <c r="C183" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="D183" t="s">
         <v>1739</v>
@@ -19259,13 +19265,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="B184" t="s">
         <v>1290</v>
       </c>
       <c r="C184" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="D184" t="s">
         <v>1739</v>
@@ -19273,13 +19279,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="B185" t="s">
         <v>22</v>
       </c>
       <c r="C185" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="D185" t="s">
         <v>330</v>
@@ -19287,13 +19293,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="B186" t="s">
         <v>22</v>
       </c>
       <c r="C186" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="D186" t="s">
         <v>330</v>
@@ -19301,13 +19307,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="B187" t="s">
         <v>27</v>
       </c>
       <c r="C187" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="D187" t="s">
         <v>330</v>
@@ -19315,13 +19321,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="B188" t="s">
         <v>26</v>
       </c>
       <c r="C188" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="D188" t="s">
         <v>330</v>
@@ -19329,13 +19335,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="B189" t="s">
         <v>23</v>
       </c>
       <c r="C189" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="D189" t="s">
         <v>330</v>
@@ -19343,13 +19349,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="B190" t="s">
         <v>24</v>
       </c>
       <c r="C190" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="D190" t="s">
         <v>330</v>
@@ -19357,13 +19363,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="B191" t="s">
         <v>22</v>
       </c>
       <c r="C191" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="D191" t="s">
         <v>330</v>
@@ -19371,13 +19377,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="B192" t="s">
         <v>27</v>
       </c>
       <c r="C192" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="D192" t="s">
         <v>1739</v>
@@ -19385,13 +19391,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="B193" t="s">
         <v>26</v>
       </c>
       <c r="C193" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="D193" t="s">
         <v>1739</v>
@@ -19399,13 +19405,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="B194" t="s">
         <v>23</v>
       </c>
       <c r="C194" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="D194" t="s">
         <v>1739</v>
@@ -19413,13 +19419,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="B195" t="s">
         <v>24</v>
       </c>
       <c r="C195" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="D195" t="s">
         <v>1739</v>
@@ -19427,13 +19433,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="B196" t="s">
         <v>22</v>
       </c>
       <c r="C196" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="D196" t="s">
         <v>1739</v>
@@ -19441,13 +19447,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="B197" t="s">
         <v>27</v>
       </c>
       <c r="C197" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="D197" t="s">
         <v>330</v>
@@ -19455,13 +19461,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="B198" t="s">
         <v>22</v>
       </c>
       <c r="C198" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="D198" t="s">
         <v>330</v>
@@ -19469,13 +19475,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="B199" t="s">
         <v>27</v>
       </c>
       <c r="C199" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="D199" t="s">
         <v>1739</v>
@@ -19483,13 +19489,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="B200" t="s">
         <v>22</v>
       </c>
       <c r="C200" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="D200" t="s">
         <v>1739</v>
@@ -19497,13 +19503,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="B201" t="s">
         <v>26</v>
       </c>
       <c r="C201" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="D201" t="s">
         <v>330</v>
@@ -19511,13 +19517,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="B202" t="s">
         <v>23</v>
       </c>
       <c r="C202" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="D202" t="s">
         <v>330</v>
@@ -19525,13 +19531,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="B203" t="s">
         <v>24</v>
       </c>
       <c r="C203" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="D203" t="s">
         <v>330</v>
@@ -19539,13 +19545,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="B204" t="s">
         <v>22</v>
       </c>
       <c r="C204" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="D204" t="s">
         <v>330</v>
@@ -19553,13 +19559,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="B205" t="s">
         <v>25</v>
       </c>
       <c r="C205" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="D205" t="s">
         <v>330</v>
@@ -19567,13 +19573,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="B206" t="s">
         <v>1290</v>
       </c>
       <c r="C206" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="D206" t="s">
         <v>330</v>
@@ -19581,13 +19587,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="B207" t="s">
         <v>26</v>
       </c>
       <c r="C207" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="D207" t="s">
         <v>1739</v>
@@ -19595,13 +19601,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="B208" t="s">
         <v>23</v>
       </c>
       <c r="C208" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="D208" t="s">
         <v>1739</v>
@@ -19609,13 +19615,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="B209" t="s">
         <v>24</v>
       </c>
       <c r="C209" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="D209" t="s">
         <v>1739</v>
@@ -19623,13 +19629,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="B210" t="s">
         <v>22</v>
       </c>
       <c r="C210" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="D210" t="s">
         <v>1739</v>
@@ -19637,13 +19643,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="B211" t="s">
         <v>26</v>
       </c>
       <c r="C211" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="D211" t="s">
         <v>330</v>
@@ -19651,13 +19657,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="B212" t="s">
         <v>23</v>
       </c>
       <c r="C212" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="D212" t="s">
         <v>330</v>
@@ -19665,13 +19671,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="B213" t="s">
         <v>24</v>
       </c>
       <c r="C213" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="D213" t="s">
         <v>330</v>
@@ -19679,13 +19685,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="B214" t="s">
         <v>22</v>
       </c>
       <c r="C214" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="D214" t="s">
         <v>330</v>
@@ -19693,13 +19699,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="B215" t="s">
         <v>25</v>
       </c>
       <c r="C215" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="D215" t="s">
         <v>330</v>
@@ -19707,13 +19713,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="B216" t="s">
         <v>26</v>
       </c>
       <c r="C216" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="D216" t="s">
         <v>1739</v>
@@ -19721,13 +19727,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="B217" t="s">
         <v>23</v>
       </c>
       <c r="C217" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="D217" t="s">
         <v>1739</v>
@@ -19735,13 +19741,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="B218" t="s">
         <v>24</v>
       </c>
       <c r="C218" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="D218" t="s">
         <v>1739</v>
@@ -19749,13 +19755,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="B219" t="s">
         <v>22</v>
       </c>
       <c r="C219" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="D219" t="s">
         <v>1739</v>
@@ -19763,13 +19769,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="B220" t="s">
         <v>23</v>
       </c>
       <c r="C220" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="D220" t="s">
         <v>330</v>
@@ -19777,13 +19783,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="B221" t="s">
         <v>24</v>
       </c>
       <c r="C221" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="D221" t="s">
         <v>330</v>
@@ -19791,13 +19797,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="B222" t="s">
         <v>23</v>
       </c>
       <c r="C222" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="D222" t="s">
         <v>1739</v>
@@ -19805,13 +19811,13 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="B223" t="s">
         <v>24</v>
       </c>
       <c r="C223" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="D223" t="s">
         <v>1739</v>
@@ -19819,13 +19825,13 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="B224" t="s">
         <v>23</v>
       </c>
       <c r="C224" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="D224" t="s">
         <v>330</v>
@@ -19833,13 +19839,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="B225" t="s">
         <v>24</v>
       </c>
       <c r="C225" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="D225" t="s">
         <v>330</v>
@@ -19847,13 +19853,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="B226" t="s">
         <v>22</v>
       </c>
       <c r="C226" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="D226" t="s">
         <v>330</v>
@@ -19861,13 +19867,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="B227" t="s">
         <v>23</v>
       </c>
       <c r="C227" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="D227" t="s">
         <v>1739</v>
@@ -19875,13 +19881,13 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="B228" t="s">
         <v>24</v>
       </c>
       <c r="C228" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="D228" t="s">
         <v>1739</v>
@@ -19889,13 +19895,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="B229" t="s">
         <v>22</v>
       </c>
       <c r="C229" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="D229" t="s">
         <v>1739</v>
@@ -19903,13 +19909,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="B230" t="s">
         <v>22</v>
       </c>
       <c r="C230" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="D230" t="s">
         <v>330</v>
@@ -19917,13 +19923,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="B231" t="s">
         <v>22</v>
       </c>
       <c r="C231" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="D231" t="s">
         <v>1739</v>
@@ -19931,13 +19937,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="B232" t="s">
         <v>26</v>
       </c>
       <c r="C232" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="D232" t="s">
         <v>330</v>
@@ -19945,13 +19951,13 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="B233" t="s">
         <v>22</v>
       </c>
       <c r="C233" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="D233" t="s">
         <v>330</v>
@@ -19959,13 +19965,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="B234" t="s">
         <v>26</v>
       </c>
       <c r="C234" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="D234" t="s">
         <v>1739</v>
@@ -19973,13 +19979,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="B235" t="s">
         <v>22</v>
       </c>
       <c r="C235" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="D235" t="s">
         <v>1739</v>
@@ -19987,13 +19993,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="B236" t="s">
         <v>22</v>
       </c>
       <c r="C236" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="D236" t="s">
         <v>330</v>
@@ -20001,13 +20007,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="B237" t="s">
         <v>22</v>
       </c>
       <c r="C237" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="D237" t="s">
         <v>1739</v>
@@ -20015,13 +20021,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="B238" t="s">
         <v>26</v>
       </c>
       <c r="C238" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="D238" t="s">
         <v>330</v>
@@ -20029,13 +20035,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="B239" t="s">
         <v>23</v>
       </c>
       <c r="C239" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="D239" t="s">
         <v>330</v>
@@ -20043,13 +20049,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="B240" t="s">
         <v>24</v>
       </c>
       <c r="C240" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="D240" t="s">
         <v>330</v>
@@ -20057,13 +20063,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="B241" t="s">
         <v>22</v>
       </c>
       <c r="C241" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="D241" t="s">
         <v>330</v>
@@ -20071,13 +20077,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="B242" t="s">
         <v>1290</v>
       </c>
       <c r="C242" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="D242" t="s">
         <v>330</v>
@@ -20085,13 +20091,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="B243" t="s">
         <v>26</v>
       </c>
       <c r="C243" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
       <c r="D243" t="s">
         <v>1739</v>
@@ -20099,13 +20105,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="B244" t="s">
         <v>23</v>
       </c>
       <c r="C244" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="D244" t="s">
         <v>1739</v>
@@ -20113,13 +20119,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="B245" t="s">
         <v>24</v>
       </c>
       <c r="C245" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="D245" t="s">
         <v>1739</v>
@@ -20127,13 +20133,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="B246" t="s">
         <v>22</v>
       </c>
       <c r="C246" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="D246" t="s">
         <v>1739</v>
@@ -20141,13 +20147,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="B247" t="s">
         <v>22</v>
       </c>
       <c r="C247" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="D247" t="s">
         <v>330</v>
@@ -20155,13 +20161,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="B248" t="s">
         <v>22</v>
       </c>
       <c r="C248" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="D248" t="s">
         <v>1739</v>
@@ -20169,13 +20175,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="B249" t="s">
         <v>22</v>
       </c>
       <c r="C249" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="D249" t="s">
         <v>330</v>
@@ -20183,13 +20189,13 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="B250" t="s">
         <v>25</v>
       </c>
       <c r="C250" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="D250" t="s">
         <v>330</v>
@@ -20197,13 +20203,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="B251" t="s">
         <v>22</v>
       </c>
       <c r="C251" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="D251" t="s">
         <v>1739</v>
@@ -20211,13 +20217,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="B252" t="s">
         <v>22</v>
       </c>
       <c r="C252" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D252" t="s">
         <v>330</v>
@@ -20225,13 +20231,13 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="B253" t="s">
         <v>22</v>
       </c>
       <c r="C253" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="D253" t="s">
         <v>1739</v>
@@ -20239,13 +20245,13 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="B254" t="s">
         <v>22</v>
       </c>
       <c r="C254" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="D254" t="s">
         <v>330</v>
@@ -20253,13 +20259,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="B255" t="s">
         <v>25</v>
       </c>
       <c r="C255" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="D255" t="s">
         <v>330</v>
@@ -20267,13 +20273,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="B256" t="s">
         <v>22</v>
       </c>
       <c r="C256" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="D256" t="s">
         <v>1739</v>
@@ -20281,13 +20287,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="B257" t="s">
         <v>22</v>
       </c>
       <c r="C257" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="D257" t="s">
         <v>330</v>
@@ -20295,13 +20301,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="B258" t="s">
         <v>22</v>
       </c>
       <c r="C258" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D258" t="s">
         <v>1739</v>
@@ -20309,13 +20315,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="B259" t="s">
         <v>27</v>
       </c>
       <c r="C259" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="D259" t="s">
         <v>330</v>
@@ -20323,13 +20329,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="B260" t="s">
         <v>27</v>
       </c>
       <c r="C260" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="D260" t="s">
         <v>330</v>
@@ -20337,13 +20343,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="B261" t="s">
         <v>27</v>
       </c>
       <c r="C261" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="D261" t="s">
         <v>1739</v>
@@ -20351,13 +20357,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="B262" t="s">
         <v>27</v>
       </c>
       <c r="C262" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="D262" t="s">
         <v>330</v>
@@ -20365,13 +20371,13 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="B263" t="s">
         <v>27</v>
       </c>
       <c r="C263" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="D263" t="s">
         <v>1739</v>
@@ -20379,13 +20385,13 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="B264" t="s">
         <v>27</v>
       </c>
       <c r="C264" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="D264" t="s">
         <v>330</v>
@@ -20393,13 +20399,13 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="B265" t="s">
         <v>27</v>
       </c>
       <c r="C265" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="D265" t="s">
         <v>1739</v>
@@ -20407,13 +20413,13 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B266" t="s">
         <v>27</v>
       </c>
       <c r="C266" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="D266" t="s">
         <v>330</v>
@@ -20421,13 +20427,13 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="B267" t="s">
         <v>27</v>
       </c>
       <c r="C267" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="D267" t="s">
         <v>1739</v>
@@ -20435,13 +20441,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="B268" t="s">
         <v>27</v>
       </c>
       <c r="C268" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="D268" t="s">
         <v>330</v>
@@ -20449,13 +20455,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="B269" t="s">
         <v>27</v>
       </c>
       <c r="C269" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="D269" t="s">
         <v>1739</v>
@@ -20463,13 +20469,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="B270" t="s">
         <v>27</v>
       </c>
       <c r="C270" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="D270" t="s">
         <v>330</v>
@@ -20477,13 +20483,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="B271" t="s">
         <v>27</v>
       </c>
       <c r="C271" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="D271" t="s">
         <v>1739</v>
@@ -20491,13 +20497,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="B272" t="s">
         <v>27</v>
       </c>
       <c r="C272" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="D272" t="s">
         <v>330</v>
@@ -20505,13 +20511,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="B273" t="s">
         <v>27</v>
       </c>
       <c r="C273" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="D273" t="s">
         <v>330</v>
@@ -20519,13 +20525,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="B274" t="s">
         <v>27</v>
       </c>
       <c r="C274" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="D274" t="s">
         <v>1739</v>
@@ -20533,13 +20539,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="B275" t="s">
         <v>27</v>
       </c>
       <c r="C275" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="D275" t="s">
         <v>330</v>
@@ -20547,13 +20553,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="B276" t="s">
         <v>27</v>
       </c>
       <c r="C276" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="D276" t="s">
         <v>1739</v>
@@ -20561,13 +20567,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="B277" t="s">
         <v>27</v>
       </c>
       <c r="C277" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="D277" t="s">
         <v>330</v>
@@ -20575,13 +20581,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="B278" t="s">
         <v>27</v>
       </c>
       <c r="C278" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="D278" t="s">
         <v>1739</v>
@@ -20589,13 +20595,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="B279" t="s">
         <v>27</v>
       </c>
       <c r="C279" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="D279" t="s">
         <v>330</v>
@@ -20603,13 +20609,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="B280" t="s">
         <v>27</v>
       </c>
       <c r="C280" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="D280" t="s">
         <v>1739</v>
@@ -20617,13 +20623,13 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="B281" t="s">
         <v>27</v>
       </c>
       <c r="C281" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="D281" t="s">
         <v>330</v>
@@ -20631,13 +20637,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="B282" t="s">
         <v>27</v>
       </c>
       <c r="C282" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="D282" t="s">
         <v>1739</v>
@@ -20645,13 +20651,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="B283" t="s">
         <v>27</v>
       </c>
       <c r="C283" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="D283" t="s">
         <v>330</v>
@@ -20659,13 +20665,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="B284" t="s">
         <v>27</v>
       </c>
       <c r="C284" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="D284" t="s">
         <v>1739</v>
@@ -20697,13 +20703,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="D2" t="s">
         <v>330</v>
@@ -20711,13 +20717,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="D3" t="s">
         <v>330</v>
@@ -20725,13 +20731,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="D4" t="s">
         <v>331</v>
@@ -20739,13 +20745,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="D5" t="s">
         <v>331</v>
@@ -20753,13 +20759,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="D6" t="s">
         <v>330</v>
@@ -20767,13 +20773,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="D7" t="s">
         <v>330</v>
@@ -20781,7 +20787,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -20795,7 +20801,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -20809,13 +20815,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="D10" t="s">
         <v>330</v>
@@ -20823,13 +20829,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="D11" t="s">
         <v>330</v>
@@ -20837,13 +20843,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="D12" t="s">
         <v>331</v>
@@ -20851,13 +20857,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="D13" t="s">
         <v>331</v>
@@ -20865,13 +20871,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="D14" t="s">
         <v>330</v>
@@ -20879,13 +20885,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="D15" t="s">
         <v>330</v>
@@ -20893,7 +20899,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
@@ -20907,7 +20913,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -20921,13 +20927,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="D18" t="s">
         <v>330</v>
@@ -20935,13 +20941,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="D19" t="s">
         <v>330</v>
@@ -20949,13 +20955,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="D20" t="s">
         <v>331</v>
@@ -20963,13 +20969,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="D21" t="s">
         <v>331</v>
@@ -20977,13 +20983,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="D22" t="s">
         <v>330</v>
@@ -20991,13 +20997,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="D23" t="s">
         <v>330</v>
@@ -21005,7 +21011,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -21019,7 +21025,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
